--- a/tests/fixtures/account_ikze_99999999_pl_xlsx_2024-12-31_2026-05-02.xlsx
+++ b/tests/fixtures/account_ikze_99999999_pl_xlsx_2024-12-31_2026-05-02.xlsx
@@ -2,44 +2,174 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="120" windowWidth="18060" windowHeight="7050" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CLOSED POSITION HISTORY" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="OPEN POSITION 02052026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PENDING ORDERS HISTORY" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PENDING ORDERS HISTORY " sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="CASH OPERATION HISTORY" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'CLOSED POSITION HISTORY'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'OPEN POSITION 02052026'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'PENDING ORDERS HISTORY '!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'CASH OPERATION HISTORY'!$1:$2</definedName>
+  </definedNames>
+  <calcPr calcId="125725" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="[$-010809]dd/mm/yyyy hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="[$-010809]0.00;(0.00)"/>
+    <numFmt numFmtId="166" formatCode="[$-010809]0.0000;(0.0000)"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font/>
+    <font>
+      <name val="Segoe UI"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <strike val="0"/>
+      <color rgb="FFD3D3D3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FFD3D3D3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <strike val="0"/>
+      <color rgb="FFD3D3D3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FFD3D3D3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FFD3D3D3"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF5CCC81"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FFFF3B2E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F4F4"/>
+        <bgColor rgb="FFF3F4F4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -47,16 +177,229 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="67">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -70,11 +413,11 @@
       <rgbColor rgb="00FF00FF"/>
       <rgbColor rgb="0000FFFF"/>
       <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00D3D3D3"/>
       <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00F3F4F4"/>
+      <rgbColor rgb="005CCC81"/>
+      <rgbColor rgb="00FF3B2E"/>
       <rgbColor rgb="00FF00FF"/>
       <rgbColor rgb="0000FFFF"/>
       <rgbColor rgb="00800000"/>
@@ -128,6 +471,306 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>424589</colOff>
+      <row>0</row>
+      <rowOff>393080</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Picture 1"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>607809</colOff>
+      <row>7</row>
+      <rowOff>546100</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>19</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>19</col>
+      <colOff>424589</colOff>
+      <row>0</row>
+      <rowOff>393080</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Picture 1"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>16</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>16</col>
+      <colOff>1558400</colOff>
+      <row>6</row>
+      <rowOff>546100</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>15</col>
+      <colOff>424589</colOff>
+      <row>0</row>
+      <rowOff>393080</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Picture 1"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>12</col>
+      <colOff>1556688</colOff>
+      <row>6</row>
+      <rowOff>546100</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>10</col>
+      <colOff>424589</colOff>
+      <row>0</row>
+      <rowOff>393080</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Picture 1"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>7</col>
+      <colOff>1473200</colOff>
+      <row>6</row>
+      <rowOff>515761</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,270 +1059,2842 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <cols>
+    <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
+    <col width="13.86328125" customWidth="1" style="49" min="2" max="2"/>
+    <col width="10.953125" customWidth="1" style="49" min="3" max="3"/>
+    <col width="7.93359375" customWidth="1" style="49" min="4" max="4"/>
+    <col width="10.78125" customWidth="1" style="49" min="5" max="5"/>
+    <col width="17.18359375" customWidth="1" style="49" min="6" max="6"/>
+    <col width="11.93359375" customWidth="1" style="49" min="7" max="7"/>
+    <col width="17.59375" customWidth="1" style="49" min="8" max="8"/>
+    <col width="13.50390625" customWidth="1" style="49" min="9" max="9"/>
+    <col width="13.4921875" customWidth="1" style="49" min="10" max="10"/>
+    <col width="13.4921875" customWidth="1" style="49" min="11" max="11"/>
+    <col width="10.921875" customWidth="1" style="49" min="12" max="12"/>
+    <col width="11.703125" customWidth="1" style="49" min="13" max="13"/>
+    <col width="11.00390625" customWidth="1" style="49" min="14" max="14"/>
+    <col width="10.80078125" customWidth="1" style="49" min="15" max="15"/>
+    <col width="11.33203125" customWidth="1" style="49" min="16" max="16"/>
+    <col width="18.953125" customWidth="1" style="49" min="17" max="17"/>
+    <col width="16.9921875" customWidth="1" style="49" min="18" max="18"/>
+    <col width="13.4921875" customWidth="1" style="49" min="19" max="19"/>
+    <col width="16.9921875" customWidth="1" style="49" min="20" max="20"/>
+    <col width="14.15234375" customWidth="1" style="49" min="21" max="21"/>
+    <col width="10.26171875" customWidth="1" style="49" min="22" max="22"/>
+    <col width="17.28125" customWidth="1" style="49" min="23" max="23"/>
+    <col width="0.0234375" customWidth="1" style="49" min="24" max="24"/>
+    <col width="2.58203125" customWidth="1" style="49" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.75" customHeight="1" s="49"/>
+    <row r="2" ht="2.25" customHeight="1" s="49"/>
+    <row r="3" ht="2.3" customHeight="1" s="49"/>
+    <row r="4" ht="25.2" customHeight="1" s="49">
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr"/>
+      <c r="D4" s="1" t="inlineStr"/>
+      <c r="E4" s="1" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Name and surname</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="50" t="n">
+        <v>46155.50146462963</v>
+      </c>
+    </row>
+    <row r="5" ht="25.2" customHeight="1" s="49">
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr"/>
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1" t="inlineStr"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="n"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="25.2" customHeight="1" s="49">
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>Free margin</t>
+        </is>
+      </c>
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>Margin level</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="25.2" customHeight="1" s="49">
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="44" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>16755.21</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="R7" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="43.2" customHeight="1" s="49">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLOSED POSITION HISTORY </t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="15" t="inlineStr"/>
+      <c r="J8" s="15" t="inlineStr"/>
+      <c r="K8" s="15" t="inlineStr"/>
+      <c r="L8" s="15" t="inlineStr"/>
+      <c r="M8" s="15" t="inlineStr"/>
+      <c r="N8" s="15" t="inlineStr"/>
+      <c r="O8" s="15" t="inlineStr"/>
+      <c r="P8" s="15" t="inlineStr"/>
+      <c r="Q8" s="15" t="inlineStr"/>
+      <c r="R8" s="15" t="inlineStr"/>
+      <c r="S8" s="15" t="inlineStr"/>
+      <c r="T8" s="15" t="inlineStr"/>
+    </row>
+    <row r="9" ht="23.75" customHeight="1" s="49">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>31/12/2024 - 02/05/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr"/>
+      <c r="G9" s="15" t="inlineStr"/>
+      <c r="H9" s="15" t="inlineStr"/>
+      <c r="I9" s="15" t="inlineStr"/>
+      <c r="J9" s="15" t="inlineStr"/>
+      <c r="K9" s="15" t="inlineStr"/>
+      <c r="L9" s="15" t="inlineStr"/>
+      <c r="M9" s="15" t="inlineStr"/>
+      <c r="N9" s="15" t="inlineStr"/>
+      <c r="O9" s="15" t="inlineStr"/>
+      <c r="P9" s="15" t="inlineStr"/>
+      <c r="Q9" s="15" t="inlineStr"/>
+      <c r="R9" s="15" t="inlineStr"/>
+      <c r="S9" s="15" t="inlineStr"/>
+      <c r="T9" s="15" t="inlineStr"/>
+      <c r="U9" s="15" t="inlineStr"/>
+    </row>
+    <row r="10" ht="17" customHeight="1" s="49">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Balance :4179.88 - 0.00</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr"/>
+      <c r="I10" s="15" t="inlineStr"/>
+      <c r="J10" s="15" t="inlineStr"/>
+      <c r="K10" s="15" t="inlineStr"/>
+      <c r="L10" s="15" t="inlineStr"/>
+      <c r="M10" s="15" t="inlineStr"/>
+      <c r="N10" s="15" t="inlineStr"/>
+      <c r="O10" s="15" t="inlineStr"/>
+      <c r="P10" s="15" t="inlineStr"/>
+      <c r="Q10" s="15" t="inlineStr"/>
+      <c r="R10" s="15" t="inlineStr"/>
+      <c r="S10" s="15" t="inlineStr"/>
+      <c r="T10" s="15" t="inlineStr"/>
+      <c r="U10" s="15" t="inlineStr"/>
+    </row>
+    <row r="11" ht="17" customHeight="1" s="49">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Open price</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Close price</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>Open origin</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>Close origin</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>Purchase value</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>Sale value</t>
+        </is>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="P11" s="18" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="Q11" s="19" t="inlineStr">
+        <is>
+          <t>Commission</t>
+        </is>
+      </c>
+      <c r="R11" s="19" t="inlineStr">
+        <is>
+          <t>Swap</t>
+        </is>
+      </c>
+      <c r="S11" s="19" t="inlineStr">
+        <is>
+          <t>Rollover</t>
+        </is>
+      </c>
+      <c r="T11" s="19" t="inlineStr">
+        <is>
+          <t>Gross P/L</t>
+        </is>
+      </c>
+      <c r="U11" s="18" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="49">
+      <c r="B12" s="22" t="n">
+        <v>900000004</v>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>ASSET07.DE</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="F12" s="53" t="n">
+        <v>45908.37810016204</v>
+      </c>
+      <c r="G12" s="52" t="n">
+        <v>1159.8</v>
+      </c>
+      <c r="H12" s="53" t="n">
+        <v>45943.37802402778</v>
+      </c>
+      <c r="I12" s="52" t="n">
+        <v>1217.2</v>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L12" s="54" t="n">
+        <v>3445.34</v>
+      </c>
+      <c r="M12" s="54" t="n">
+        <v>3589.26</v>
+      </c>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="56" t="n">
+        <v>143.92</v>
+      </c>
+      <c r="U12" s="22" t="n"/>
+      <c r="V12" s="57" t="n"/>
+      <c r="W12" s="57" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="49">
+      <c r="B13" s="31" t="n">
+        <v>900000005</v>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>ASSET03.UK</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E13" s="58" t="n">
+        <v>14</v>
+      </c>
+      <c r="F13" s="59" t="n">
+        <v>45901.37525900463</v>
+      </c>
+      <c r="G13" s="58" t="n">
+        <v>72.69</v>
+      </c>
+      <c r="H13" s="59" t="n">
+        <v>45951.64296587963</v>
+      </c>
+      <c r="I13" s="58" t="n">
+        <v>83.76000000000001</v>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L13" s="60" t="n">
+        <v>3717.31</v>
+      </c>
+      <c r="M13" s="60" t="n">
+        <v>4258.56</v>
+      </c>
+      <c r="N13" s="31" t="n"/>
+      <c r="O13" s="31" t="n"/>
+      <c r="P13" s="31" t="n"/>
+      <c r="Q13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="62" t="n">
+        <v>541.25</v>
+      </c>
+      <c r="U13" s="31" t="n"/>
+      <c r="V13" s="57" t="n"/>
+      <c r="W13" s="57" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="49">
+      <c r="B14" s="22" t="n">
+        <v>900000006</v>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="53" t="n">
+        <v>46024.4274031713</v>
+      </c>
+      <c r="G14" s="52" t="n">
+        <v>499</v>
+      </c>
+      <c r="H14" s="53" t="n">
+        <v>46073.64598782407</v>
+      </c>
+      <c r="I14" s="52" t="n">
+        <v>458.2</v>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L14" s="54" t="n">
+        <v>1996</v>
+      </c>
+      <c r="M14" s="54" t="n">
+        <v>1832.8</v>
+      </c>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="63" t="n">
+        <v>-163.2</v>
+      </c>
+      <c r="U14" s="22" t="n"/>
+      <c r="V14" s="57" t="n"/>
+      <c r="W14" s="57" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="49">
+      <c r="B15" s="31" t="n">
+        <v>900000007</v>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>ASSET06.PL</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E15" s="58" t="n">
+        <v>35</v>
+      </c>
+      <c r="F15" s="59" t="n">
+        <v>45891.3750000463</v>
+      </c>
+      <c r="G15" s="58" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="H15" s="59" t="n">
+        <v>46084.37692043981</v>
+      </c>
+      <c r="I15" s="58" t="n">
+        <v>64.73999999999999</v>
+      </c>
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K15" s="31" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L15" s="60" t="n">
+        <v>2268</v>
+      </c>
+      <c r="M15" s="60" t="n">
+        <v>2265.9</v>
+      </c>
+      <c r="N15" s="31" t="n"/>
+      <c r="O15" s="31" t="n"/>
+      <c r="P15" s="31" t="n"/>
+      <c r="Q15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="64" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="U15" s="31" t="n"/>
+      <c r="V15" s="57" t="n"/>
+      <c r="W15" s="57" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1" s="49">
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="inlineStr"/>
+      <c r="D16" s="39" t="inlineStr"/>
+      <c r="E16" s="39" t="inlineStr"/>
+      <c r="F16" s="39" t="inlineStr"/>
+      <c r="G16" s="39" t="inlineStr"/>
+      <c r="H16" s="39" t="inlineStr"/>
+      <c r="I16" s="39" t="inlineStr"/>
+      <c r="J16" s="39" t="inlineStr"/>
+      <c r="K16" s="39" t="inlineStr"/>
+      <c r="L16" s="39" t="inlineStr"/>
+      <c r="M16" s="39" t="inlineStr"/>
+      <c r="N16" s="39" t="inlineStr"/>
+      <c r="O16" s="39" t="inlineStr"/>
+      <c r="P16" s="39" t="inlineStr"/>
+      <c r="Q16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="45" t="n">
+        <v>519.87</v>
+      </c>
+      <c r="U16" s="39" t="inlineStr"/>
+    </row>
+    <row r="17" ht="0.05" customHeight="1" s="49"/>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="U8:X8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="U7:W7"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="U5:W5"/>
+    <mergeCell ref="U10:W10"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="U6:W6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="R6:T6"/>
+  </mergeCells>
+  <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="1.36888188976378" header="0.393700787401575" footer="0.393700787401575"/>
+  <pageSetup orientation="landscape" paperSize="0" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0">
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Segoe UI,Regular"&amp;10 &amp;P </oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:P10"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
+    <col width="13.86328125" customWidth="1" style="49" min="2" max="2"/>
+    <col width="10.953125" customWidth="1" style="49" min="3" max="3"/>
+    <col width="7.93359375" customWidth="1" style="49" min="4" max="4"/>
+    <col width="10.78125" customWidth="1" style="49" min="5" max="5"/>
+    <col width="17.32421875" customWidth="1" style="49" min="6" max="6"/>
+    <col width="11.93359375" customWidth="1" style="49" min="7" max="7"/>
+    <col width="17.59375" customWidth="1" style="49" min="8" max="8"/>
+    <col width="13.50390625" customWidth="1" style="49" min="9" max="9"/>
+    <col width="13.4921875" customWidth="1" style="49" min="10" max="10"/>
+    <col width="13.4921875" customWidth="1" style="49" min="11" max="11"/>
+    <col width="10.921875" customWidth="1" style="49" min="12" max="12"/>
+    <col width="22.703125" customWidth="1" style="49" min="13" max="13"/>
+    <col width="22.1328125" customWidth="1" style="49" min="14" max="14"/>
+    <col width="13.4921875" customWidth="1" style="49" min="15" max="15"/>
+    <col width="18.953125" customWidth="1" style="49" min="16" max="16"/>
+    <col width="33.97265625" customWidth="1" style="49" min="17" max="17"/>
+    <col width="0.0234375" customWidth="1" style="49" min="18" max="18"/>
+    <col width="14.01171875" customWidth="1" style="49" min="19" max="19"/>
+    <col width="10.26171875" customWidth="1" style="49" min="20" max="20"/>
+    <col width="19.87109375" customWidth="1" style="49" min="21" max="21"/>
+  </cols>
   <sheetData>
-    <row r="3">
-      <c r="B3" s="1" t="n">
-        <v>46144.4375</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="D4" t="inlineStr">
+    <row r="1" ht="31.75" customHeight="1" s="49"/>
+    <row r="2" ht="2.25" customHeight="1" s="49"/>
+    <row r="3" ht="25.2" customHeight="1" s="49">
+      <c r="B3" s="13" t="inlineStr"/>
+      <c r="C3" s="13" t="inlineStr"/>
+      <c r="D3" s="13" t="inlineStr"/>
+      <c r="E3" s="13" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Name and surname</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="inlineStr"/>
+      <c r="O3" s="15" t="inlineStr"/>
+      <c r="P3" s="15" t="inlineStr"/>
+      <c r="Q3" s="50" t="n">
+        <v>46155.501465</v>
+      </c>
+    </row>
+    <row r="4" ht="25.2" customHeight="1" s="49">
+      <c r="B4" s="13" t="inlineStr"/>
+      <c r="C4" s="13" t="inlineStr"/>
+      <c r="D4" s="13" t="inlineStr"/>
+      <c r="E4" s="13" t="inlineStr"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="n"/>
+      <c r="N4" s="15" t="inlineStr"/>
+      <c r="O4" s="15" t="inlineStr"/>
+      <c r="P4" s="15" t="inlineStr"/>
+      <c r="Q4" s="15" t="inlineStr"/>
+    </row>
+    <row r="5" ht="25.2" customHeight="1" s="49">
+      <c r="B5" s="13" t="inlineStr"/>
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="13" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="D5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>Free margin</t>
+        </is>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>Margin level</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.2" customHeight="1" s="49">
+      <c r="B6" s="13" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="13" t="inlineStr"/>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="44" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>16755.21</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="Q6" s="51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="43.2" customHeight="1" s="49">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN POSITION HISTORY </t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="15" t="inlineStr"/>
+      <c r="J7" s="15" t="inlineStr"/>
+      <c r="K7" s="15" t="inlineStr"/>
+      <c r="L7" s="15" t="inlineStr"/>
+      <c r="M7" s="15" t="inlineStr"/>
+      <c r="N7" s="15" t="inlineStr"/>
+      <c r="O7" s="15" t="inlineStr"/>
+      <c r="P7" s="15" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.75" customHeight="1" s="49">
+      <c r="B8" s="65" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F8" s="15" t="inlineStr"/>
+      <c r="G8" s="15" t="inlineStr"/>
+      <c r="H8" s="15" t="inlineStr"/>
+      <c r="I8" s="15" t="inlineStr"/>
+      <c r="J8" s="15" t="inlineStr"/>
+      <c r="K8" s="15" t="inlineStr"/>
+      <c r="L8" s="15" t="inlineStr"/>
+      <c r="M8" s="15" t="inlineStr"/>
+      <c r="N8" s="15" t="inlineStr"/>
+      <c r="O8" s="15" t="inlineStr"/>
+      <c r="P8" s="15" t="inlineStr"/>
+      <c r="Q8" s="15" t="inlineStr"/>
+    </row>
+    <row r="9" ht="17" customHeight="1" s="49">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>Open time</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>Open price</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>Market price</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>Purchase value</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L9" s="18" t="inlineStr">
         <is>
           <t>Margin</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M9" s="19" t="inlineStr">
         <is>
           <t>Commission</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N9" s="19" t="inlineStr">
         <is>
           <t>Swap</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>Rollover</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr">
         <is>
           <t>Gross P/L</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q9" s="18" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1000000001</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>VWCE.DE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="49">
+      <c r="B10" s="22" t="n">
+        <v>900000017</v>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>ASSET05.PL</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46132.375</v>
-      </c>
-      <c r="F8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G8" t="n">
-        <v>110</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I8" t="n">
-        <v>90</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>100</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1000000002</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CNDX.UK</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="E10" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="53" t="n">
+        <v>46086.42805099537</v>
+      </c>
+      <c r="G10" s="52" t="n">
+        <v>118.74</v>
+      </c>
+      <c r="H10" s="52" t="n">
+        <v>133.76</v>
+      </c>
+      <c r="I10" s="54" t="n">
+        <v>1187.4</v>
+      </c>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="56" t="n">
+        <v>150.2</v>
+      </c>
+      <c r="Q10" s="22" t="inlineStr"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="49">
+      <c r="B11" s="31" t="n">
+        <v>900000018</v>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46142.375</v>
-      </c>
-      <c r="F9" t="n">
-        <v>200</v>
-      </c>
-      <c r="G9" t="n">
-        <v>190</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I9" t="n">
-        <v>180</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-100</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="E11" s="58" t="n">
+        <v>5.9113</v>
+      </c>
+      <c r="F11" s="59" t="n">
+        <v>46044.64063415509</v>
+      </c>
+      <c r="G11" s="58" t="n">
+        <v>39.995</v>
+      </c>
+      <c r="H11" s="58" t="n">
+        <v>41.185</v>
+      </c>
+      <c r="I11" s="60" t="n">
+        <v>1000.02</v>
+      </c>
+      <c r="J11" s="31" t="n"/>
+      <c r="K11" s="31" t="n"/>
+      <c r="L11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="62" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="Q11" s="31" t="inlineStr"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="49">
+      <c r="B12" s="22" t="n">
+        <v>900000019</v>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="n">
+        <v>5.8645</v>
+      </c>
+      <c r="F12" s="53" t="n">
+        <v>46056.42355761574</v>
+      </c>
+      <c r="G12" s="52" t="n">
+        <v>40.205</v>
+      </c>
+      <c r="H12" s="52" t="n">
+        <v>41.185</v>
+      </c>
+      <c r="I12" s="54" t="n">
+        <v>1000.02</v>
+      </c>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="22" t="n"/>
+      <c r="L12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="56" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="Q12" s="22" t="inlineStr"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="49">
+      <c r="B13" s="31" t="n">
+        <v>900000020</v>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E13" s="58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="59" t="n">
+        <v>45908.4788880324</v>
+      </c>
+      <c r="G13" s="58" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H13" s="58" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="I13" s="60" t="n">
+        <v>154</v>
+      </c>
+      <c r="J13" s="31" t="n"/>
+      <c r="K13" s="31" t="n"/>
+      <c r="L13" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="64" t="n">
+        <v>-40.8</v>
+      </c>
+      <c r="Q13" s="31" t="inlineStr"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="49">
+      <c r="B14" s="22" t="n">
+        <v>900000021</v>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="n">
+        <v>6.0709</v>
+      </c>
+      <c r="F14" s="53" t="n">
+        <v>45950.43493203704</v>
+      </c>
+      <c r="G14" s="52" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="H14" s="52" t="n">
+        <v>41.185</v>
+      </c>
+      <c r="I14" s="54" t="n">
+        <v>999.97</v>
+      </c>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="56" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="Q14" s="22" t="inlineStr"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="49">
+      <c r="B15" s="31" t="n">
+        <v>900000022</v>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>ASSET01.PL</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E15" s="58" t="n">
+        <v>29</v>
+      </c>
+      <c r="F15" s="59" t="n">
+        <v>45896.37847430556</v>
+      </c>
+      <c r="G15" s="58" t="n">
+        <v>127.46</v>
+      </c>
+      <c r="H15" s="58" t="n">
+        <v>143.58</v>
+      </c>
+      <c r="I15" s="60" t="n">
+        <v>3696.34</v>
+      </c>
+      <c r="J15" s="31" t="n"/>
+      <c r="K15" s="31" t="n"/>
+      <c r="L15" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="62" t="n">
+        <v>467.48</v>
+      </c>
+      <c r="Q15" s="31" t="inlineStr"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="49">
+      <c r="B16" s="22" t="n">
+        <v>900000023</v>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E16" s="52" t="n">
+        <v>2.1043</v>
+      </c>
+      <c r="F16" s="53" t="n">
+        <v>46041.4602808912</v>
+      </c>
+      <c r="G16" s="52" t="n">
+        <v>475.2</v>
+      </c>
+      <c r="H16" s="52" t="n">
+        <v>437.1</v>
+      </c>
+      <c r="I16" s="54" t="n">
+        <v>999.96</v>
+      </c>
+      <c r="J16" s="22" t="n"/>
+      <c r="K16" s="22" t="n"/>
+      <c r="L16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="63" t="n">
+        <v>-80.17</v>
+      </c>
+      <c r="Q16" s="22" t="inlineStr"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="49">
+      <c r="B17" s="31" t="n">
+        <v>900000024</v>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E17" s="58" t="n">
+        <v>64</v>
+      </c>
+      <c r="F17" s="59" t="n">
+        <v>45891.37779449074</v>
+      </c>
+      <c r="G17" s="58" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="H17" s="58" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="I17" s="60" t="n">
+        <v>2336</v>
+      </c>
+      <c r="J17" s="31" t="n"/>
+      <c r="K17" s="31" t="n"/>
+      <c r="L17" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="64" t="n">
+        <v>-524.8</v>
+      </c>
+      <c r="Q17" s="31" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="49">
+      <c r="B18" s="22" t="n">
+        <v>900000025</v>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E18" s="52" t="n">
+        <v>2.1008</v>
+      </c>
+      <c r="F18" s="53" t="n">
+        <v>46120.40263733796</v>
+      </c>
+      <c r="G18" s="52" t="n">
+        <v>476</v>
+      </c>
+      <c r="H18" s="52" t="n">
+        <v>437.1</v>
+      </c>
+      <c r="I18" s="54" t="n">
+        <v>999.98</v>
+      </c>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="63" t="n">
+        <v>-81.72</v>
+      </c>
+      <c r="Q18" s="22" t="inlineStr"/>
+    </row>
+    <row r="19" ht="17" customHeight="1" s="49">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
+      <c r="C19" s="39" t="inlineStr"/>
+      <c r="D19" s="39" t="inlineStr"/>
+      <c r="E19" s="39" t="inlineStr"/>
+      <c r="F19" s="39" t="inlineStr"/>
+      <c r="G19" s="39" t="inlineStr"/>
+      <c r="H19" s="39" t="inlineStr"/>
+      <c r="I19" s="39" t="inlineStr"/>
+      <c r="J19" s="39" t="inlineStr"/>
+      <c r="K19" s="39" t="inlineStr"/>
+      <c r="L19" s="39" t="inlineStr"/>
+      <c r="M19" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="45" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="Q19" s="39" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="17">
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="I6:K6"/>
+  </mergeCells>
+  <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="1.36888188976378" header="0.393700787401575" footer="0.393700787401575"/>
+  <pageSetup orientation="landscape" paperSize="0" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0">
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Segoe UI,Regular"&amp;10 &amp;P </oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <cols>
+    <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
+    <col width="13.86328125" customWidth="1" style="49" min="2" max="2"/>
+    <col width="30.00390625" customWidth="1" style="49" min="3" max="3"/>
+    <col width="15.32421875" customWidth="1" style="49" min="4" max="4"/>
+    <col width="11.6015625" customWidth="1" style="49" min="5" max="5"/>
+    <col width="17.59375" customWidth="1" style="49" min="6" max="6"/>
+    <col width="13.4921875" customWidth="1" style="49" min="7" max="7"/>
+    <col width="13.50390625" customWidth="1" style="49" min="8" max="8"/>
+    <col width="13.4921875" customWidth="1" style="49" min="9" max="9"/>
+    <col width="10.921875" customWidth="1" style="49" min="10" max="10"/>
+    <col width="22.703125" customWidth="1" style="49" min="11" max="11"/>
+    <col width="22.1328125" customWidth="1" style="49" min="12" max="12"/>
+    <col width="52.921875" customWidth="1" style="49" min="13" max="13"/>
+    <col width="0.0234375" customWidth="1" style="49" min="14" max="14"/>
+    <col width="29.50390625" customWidth="1" style="49" min="15" max="15"/>
+    <col width="10.26171875" customWidth="1" style="49" min="16" max="16"/>
+    <col width="19.87109375" customWidth="1" style="49" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.75" customHeight="1" s="49"/>
+    <row r="2" ht="2.25" customHeight="1" s="49"/>
+    <row r="3" ht="25.2" customHeight="1" s="49">
+      <c r="B3" s="13" t="inlineStr"/>
+      <c r="C3" s="13" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Name and surname</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="L3" s="42" t="inlineStr"/>
+      <c r="M3" s="66" t="n">
+        <v>46155.50146517361</v>
+      </c>
+    </row>
+    <row r="4" ht="25.2" customHeight="1" s="49">
+      <c r="B4" s="13" t="inlineStr"/>
+      <c r="C4" s="13" t="inlineStr"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n"/>
+      <c r="L4" s="42" t="inlineStr"/>
+      <c r="M4" s="42" t="inlineStr"/>
+    </row>
+    <row r="5" ht="25.2" customHeight="1" s="49">
+      <c r="B5" s="13" t="inlineStr"/>
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Free margin</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>Margin level</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.2" customHeight="1" s="49">
+      <c r="B6" s="13" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="44" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>16755.21</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="M6" s="51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="43.2" customHeight="1" s="49">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING ORDERS HISTORY </t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="42" t="inlineStr"/>
+      <c r="H7" s="42" t="inlineStr"/>
+      <c r="I7" s="42" t="inlineStr"/>
+      <c r="J7" s="42" t="inlineStr"/>
+      <c r="K7" s="42" t="inlineStr"/>
+      <c r="L7" s="42" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.75" customHeight="1" s="49">
+      <c r="B8" s="65" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D8" s="44" t="inlineStr"/>
+      <c r="E8" s="44" t="inlineStr"/>
+      <c r="F8" s="44" t="inlineStr"/>
+      <c r="G8" s="44" t="inlineStr"/>
+      <c r="H8" s="44" t="inlineStr"/>
+      <c r="I8" s="44" t="inlineStr"/>
+      <c r="J8" s="44" t="inlineStr"/>
+      <c r="K8" s="44" t="inlineStr"/>
+      <c r="L8" s="44" t="inlineStr"/>
+      <c r="M8" s="44" t="inlineStr"/>
+    </row>
+    <row r="9" ht="17" customHeight="1" s="49">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Purchase value</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Nominal Value</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="49">
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+    </row>
+    <row r="11" ht="17" customHeight="1" s="49">
+      <c r="B11" s="39" t="inlineStr"/>
+      <c r="C11" s="45" t="inlineStr"/>
+      <c r="D11" s="45" t="inlineStr"/>
+      <c r="E11" s="45" t="inlineStr"/>
+      <c r="F11" s="45" t="inlineStr"/>
+      <c r="G11" s="45" t="inlineStr"/>
+      <c r="H11" s="45" t="inlineStr"/>
+      <c r="I11" s="45" t="inlineStr"/>
+      <c r="J11" s="45" t="inlineStr"/>
+      <c r="K11" s="45" t="inlineStr"/>
+      <c r="L11" s="45" t="inlineStr"/>
+      <c r="M11" s="45" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="B8:C8"/>
+  </mergeCells>
+  <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="1.36888188976378" header="0.393700787401575" footer="0.393700787401575"/>
+  <pageSetup orientation="landscape" paperSize="0" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0">
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Segoe UI,Regular"&amp;10 &amp;P </oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <cols>
+    <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
+    <col width="13.86328125" customWidth="1" style="49" min="2" max="2"/>
+    <col width="29.6640625" customWidth="1" style="49" min="3" max="3"/>
+    <col width="27.25390625" customWidth="1" style="49" min="4" max="4"/>
+    <col width="31.08203125" customWidth="1" style="49" min="5" max="5"/>
+    <col width="27.00390625" customWidth="1" style="49" min="6" max="6"/>
+    <col width="33.62109375" customWidth="1" style="49" min="7" max="7"/>
+    <col width="22.12109375" customWidth="1" style="49" min="8" max="8"/>
+    <col width="0.0234375" customWidth="1" style="49" min="9" max="9"/>
+    <col width="82.43359375" customWidth="1" style="49" min="10" max="10"/>
+    <col width="10.26171875" customWidth="1" style="49" min="11" max="11"/>
+    <col width="19.87109375" customWidth="1" style="49" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.75" customHeight="1" s="49"/>
+    <row r="2" ht="2.25" customHeight="1" s="49"/>
+    <row r="3" ht="25.2" customHeight="1" s="49">
+      <c r="B3" s="13" t="inlineStr"/>
+      <c r="C3" s="13" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Name and surname</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="50" t="n">
+        <v>46155.50146535879</v>
+      </c>
+    </row>
+    <row r="4" ht="25.2" customHeight="1" s="49">
+      <c r="B4" s="13" t="inlineStr"/>
+      <c r="C4" s="13" t="inlineStr"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="25.2" customHeight="1" s="49">
+      <c r="B5" s="13" t="inlineStr"/>
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Free margin</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Margin level</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.2" customHeight="1" s="49">
+      <c r="B6" s="13" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="44" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>16755.21</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="H6" s="51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="43.2" customHeight="1" s="49">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASH OPERATION HISTORY </t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="15" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.75" customHeight="1" s="49">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>31/12/2024 - 02/05/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr"/>
+      <c r="F8" s="15" t="inlineStr"/>
+      <c r="G8" s="15" t="inlineStr"/>
+      <c r="H8" s="15" t="inlineStr"/>
+    </row>
+    <row r="9" ht="17" customHeight="1" s="49">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="49">
+      <c r="B10" s="22" t="n">
+        <v>905356718</v>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>IKZE Deposit</t>
+        </is>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>45884.5093331713</v>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Transfer in operation on account with id 99999999</t>
+        </is>
+      </c>
+      <c r="F10" s="46" t="n"/>
+      <c r="G10" s="56" t="n">
+        <v>15611.4</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="49">
+      <c r="B11" s="31" t="n">
+        <v>910920026</v>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D11" s="59" t="n">
+        <v>45891.37500146991</v>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 35 @ 64.80</t>
+        </is>
+      </c>
+      <c r="F11" s="47" t="inlineStr">
+        <is>
+          <t>ASSET06.PL</t>
+        </is>
+      </c>
+      <c r="G11" s="64" t="n">
+        <v>-2268</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="49">
+      <c r="B12" s="22" t="n">
+        <v>910937823</v>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D12" s="53" t="n">
+        <v>45891.37779451389</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 64 @ 36.50</t>
+        </is>
+      </c>
+      <c r="F12" s="46" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="G12" s="63" t="n">
+        <v>-2336</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="49">
+      <c r="B13" s="31" t="n">
+        <v>914908081</v>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D13" s="59" t="n">
+        <v>45896.3784743287</v>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 29 @ 127.46</t>
+        </is>
+      </c>
+      <c r="F13" s="47" t="inlineStr">
+        <is>
+          <t>ASSET01.PL</t>
+        </is>
+      </c>
+      <c r="G13" s="64" t="n">
+        <v>-3696.34</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="49">
+      <c r="B14" s="22" t="n">
+        <v>918882470</v>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D14" s="53" t="n">
+        <v>45901.37532741898</v>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 14 @ 72.6900</t>
+        </is>
+      </c>
+      <c r="F14" s="46" t="inlineStr">
+        <is>
+          <t>ASSET03.UK</t>
+        </is>
+      </c>
+      <c r="G14" s="63" t="n">
+        <v>-3717.31</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="49">
+      <c r="B15" s="31" t="n">
+        <v>923989037</v>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D15" s="59" t="n">
+        <v>45903.72320255787</v>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2025-08</t>
+        </is>
+      </c>
+      <c r="F15" s="47" t="n"/>
+      <c r="G15" s="62" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="49">
+      <c r="B16" s="22" t="n">
+        <v>927390456</v>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D16" s="53" t="n">
+        <v>45908.37810153935</v>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.6956 @ 1159.80</t>
+        </is>
+      </c>
+      <c r="F16" s="46" t="inlineStr">
+        <is>
+          <t>ASSET07.DE</t>
+        </is>
+      </c>
+      <c r="G16" s="63" t="n">
+        <v>-3445.34</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="49">
+      <c r="B17" s="31" t="n">
+        <v>927604217</v>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D17" s="59" t="n">
+        <v>45908.47888804398</v>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 4 @ 38.50</t>
+        </is>
+      </c>
+      <c r="F17" s="47" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="G17" s="64" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="49">
+      <c r="B18" s="22" t="n">
+        <v>959579808</v>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D18" s="53" t="n">
+        <v>45933.61075918982</v>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2025-09</t>
+        </is>
+      </c>
+      <c r="F18" s="46" t="n"/>
+      <c r="G18" s="56" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="49">
+      <c r="B19" s="31" t="n">
+        <v>968431370</v>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>DIVIDENT</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="n">
+        <v>45940.49932527778</v>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>ASSET02.PL PLN 3.1400/ SHR</t>
+        </is>
+      </c>
+      <c r="F19" s="47" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="G19" s="62" t="n">
+        <v>200.96</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="49">
+      <c r="B20" s="22" t="n">
+        <v>968437404</v>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>DIVIDENT</t>
+        </is>
+      </c>
+      <c r="D20" s="53" t="n">
+        <v>45940.49933228009</v>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>ASSET02.PL PLN 3.1400/ SHR</t>
+        </is>
+      </c>
+      <c r="F20" s="46" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="G20" s="56" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="49">
+      <c r="B21" s="31" t="n">
+        <v>970656246</v>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>close trade</t>
+        </is>
+      </c>
+      <c r="D21" s="59" t="n">
+        <v>45943.37802598379</v>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>Profit of position #2011826186</t>
+        </is>
+      </c>
+      <c r="F21" s="47" t="inlineStr">
+        <is>
+          <t>ASSET07.DE</t>
+        </is>
+      </c>
+      <c r="G21" s="62" t="n">
+        <v>143.92</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="49">
+      <c r="B22" s="22" t="n">
+        <v>970656247</v>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Stock sale</t>
+        </is>
+      </c>
+      <c r="D22" s="53" t="n">
+        <v>45943.37802598379</v>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>CLOSE BUY 0.6956 @ 1217.20</t>
+        </is>
+      </c>
+      <c r="F22" s="46" t="inlineStr">
+        <is>
+          <t>ASSET07.DE</t>
+        </is>
+      </c>
+      <c r="G22" s="56" t="n">
+        <v>3445.34</v>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="49">
+      <c r="B23" s="31" t="n">
+        <v>976545654</v>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>DIVIDENT</t>
+        </is>
+      </c>
+      <c r="D23" s="59" t="n">
+        <v>45946.33076096065</v>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>ASSET06.PL PLN 4.4700/ SHR</t>
+        </is>
+      </c>
+      <c r="F23" s="47" t="inlineStr">
+        <is>
+          <t>ASSET06.PL</t>
+        </is>
+      </c>
+      <c r="G23" s="62" t="n">
+        <v>156.45</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="49">
+      <c r="B24" s="22" t="n">
+        <v>981353624</v>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D24" s="53" t="n">
+        <v>45950.43494649306</v>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 6/6.0709 @ 38.640</t>
+        </is>
+      </c>
+      <c r="F24" s="46" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="n">
+        <v>-988.29</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="49">
+      <c r="B25" s="31" t="n">
+        <v>981353594</v>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D25" s="59" t="n">
+        <v>45950.43493204861</v>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.0709/6.0709 @ 38.640</t>
+        </is>
+      </c>
+      <c r="F25" s="47" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G25" s="64" t="n">
+        <v>-11.68</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="49">
+      <c r="B26" s="22" t="n">
+        <v>983646089</v>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>close trade</t>
+        </is>
+      </c>
+      <c r="D26" s="53" t="n">
+        <v>45951.64297008102</v>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Profit of position #1999508307</t>
+        </is>
+      </c>
+      <c r="F26" s="46" t="inlineStr">
+        <is>
+          <t>ASSET03.UK</t>
+        </is>
+      </c>
+      <c r="G26" s="56" t="n">
+        <v>541.25</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="49">
+      <c r="B27" s="31" t="n">
+        <v>983646090</v>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>Stock sale</t>
+        </is>
+      </c>
+      <c r="D27" s="59" t="n">
+        <v>45951.64297008102</v>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>CLOSE BUY 14 @ 83.7600</t>
+        </is>
+      </c>
+      <c r="F27" s="47" t="inlineStr">
+        <is>
+          <t>ASSET03.UK</t>
+        </is>
+      </c>
+      <c r="G27" s="62" t="n">
+        <v>3717.31</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="49">
+      <c r="B28" s="22" t="n">
+        <v>1005869298</v>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D28" s="53" t="n">
+        <v>45967.52538728009</v>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2025-10</t>
+        </is>
+      </c>
+      <c r="F28" s="46" t="n"/>
+      <c r="G28" s="56" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="49">
+      <c r="B29" s="31" t="n">
+        <v>1039472399</v>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D29" s="59" t="n">
+        <v>45995.6207953125</v>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2025-11</t>
+        </is>
+      </c>
+      <c r="F29" s="47" t="n"/>
+      <c r="G29" s="62" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="49">
+      <c r="B30" s="22" t="n">
+        <v>1071382341</v>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D30" s="53" t="n">
+        <v>46024.42740359954</v>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 4 @ 499.00</t>
+        </is>
+      </c>
+      <c r="F30" s="46" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="n">
+        <v>-1996</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="49">
+      <c r="B31" s="31" t="n">
+        <v>1078775992</v>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D31" s="59" t="n">
+        <v>46029.59267013889</v>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2025-12</t>
+        </is>
+      </c>
+      <c r="F31" s="47" t="n"/>
+      <c r="G31" s="62" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="49">
+      <c r="B32" s="22" t="n">
+        <v>1095495643</v>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D32" s="53" t="n">
+        <v>46041.46028091435</v>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.1043/2.1043 @ 475.20</t>
+        </is>
+      </c>
+      <c r="F32" s="46" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G32" s="63" t="n">
+        <v>-49.56</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" s="49">
+      <c r="B33" s="31" t="n">
+        <v>1095495644</v>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D33" s="59" t="n">
+        <v>46041.46028163195</v>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 2/2.1043 @ 475.20</t>
+        </is>
+      </c>
+      <c r="F33" s="47" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G33" s="64" t="n">
+        <v>-950.4</v>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" s="49">
+      <c r="B34" s="22" t="n">
+        <v>1101693553</v>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D34" s="53" t="n">
+        <v>46044.64063416667</v>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.9113/5.9113 @ 39.995</t>
+        </is>
+      </c>
+      <c r="F34" s="46" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G34" s="63" t="n">
+        <v>-154.17</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="49">
+      <c r="B35" s="31" t="n">
+        <v>1101693625</v>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D35" s="59" t="n">
+        <v>46044.64064701389</v>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 5/5.9113 @ 39.995</t>
+        </is>
+      </c>
+      <c r="F35" s="47" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G35" s="64" t="n">
+        <v>-845.85</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="49">
+      <c r="B36" s="22" t="n">
+        <v>1120498401</v>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D36" s="53" t="n">
+        <v>46056.42355762731</v>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.8645/5.8645 @ 40.205</t>
+        </is>
+      </c>
+      <c r="F36" s="46" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G36" s="63" t="n">
+        <v>-147.42</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="49">
+      <c r="B37" s="31" t="n">
+        <v>1120498427</v>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D37" s="59" t="n">
+        <v>46056.4235774074</v>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 5/5.8645 @ 40.205</t>
+        </is>
+      </c>
+      <c r="F37" s="47" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G37" s="64" t="n">
+        <v>-852.61</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" s="49">
+      <c r="B38" s="22" t="n">
+        <v>1122946080</v>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D38" s="53" t="n">
+        <v>46056.83267230324</v>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2026-01</t>
+        </is>
+      </c>
+      <c r="F38" s="46" t="n"/>
+      <c r="G38" s="56" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="49">
+      <c r="B39" s="31" t="n">
+        <v>1144927775</v>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>close trade</t>
+        </is>
+      </c>
+      <c r="D39" s="59" t="n">
+        <v>46073.6459884838</v>
+      </c>
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>Profit of position #2263464366</t>
+        </is>
+      </c>
+      <c r="F39" s="47" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G39" s="64" t="n">
+        <v>-163.2</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" s="49">
+      <c r="B40" s="22" t="n">
+        <v>1144927776</v>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>Stock sale</t>
+        </is>
+      </c>
+      <c r="D40" s="53" t="n">
+        <v>46073.6459884838</v>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>CLOSE BUY 4 @ 458.20</t>
+        </is>
+      </c>
+      <c r="F40" s="46" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G40" s="56" t="n">
+        <v>1996</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="49">
+      <c r="B41" s="31" t="n">
+        <v>1157155509</v>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>close trade</t>
+        </is>
+      </c>
+      <c r="D41" s="59" t="n">
+        <v>46084.37692292824</v>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>Profit of position #1985596610</t>
+        </is>
+      </c>
+      <c r="F41" s="47" t="inlineStr">
+        <is>
+          <t>ASSET06.PL</t>
+        </is>
+      </c>
+      <c r="G41" s="64" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="49">
+      <c r="B42" s="22" t="n">
+        <v>1157155510</v>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>Stock sale</t>
+        </is>
+      </c>
+      <c r="D42" s="53" t="n">
+        <v>46084.37692292824</v>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>CLOSE BUY 35 @ 64.74</t>
+        </is>
+      </c>
+      <c r="F42" s="46" t="inlineStr">
+        <is>
+          <t>ASSET06.PL</t>
+        </is>
+      </c>
+      <c r="G42" s="56" t="n">
+        <v>2268</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="49">
+      <c r="B43" s="31" t="n">
+        <v>1162320718</v>
+      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D43" s="59" t="n">
+        <v>46086.12203777778</v>
+      </c>
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2026-02</t>
+        </is>
+      </c>
+      <c r="F43" s="47" t="n"/>
+      <c r="G43" s="62" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="49">
+      <c r="B44" s="22" t="n">
+        <v>1163175003</v>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D44" s="53" t="n">
+        <v>46086.42805105324</v>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 10 @ 118.74</t>
+        </is>
+      </c>
+      <c r="F44" s="46" t="inlineStr">
+        <is>
+          <t>ASSET05.PL</t>
+        </is>
+      </c>
+      <c r="G44" s="63" t="n">
+        <v>-1187.4</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" s="49">
+      <c r="B45" s="31" t="n">
+        <v>1208692466</v>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D45" s="59" t="n">
+        <v>46115.74372440972</v>
+      </c>
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2026-03</t>
+        </is>
+      </c>
+      <c r="F45" s="47" t="n"/>
+      <c r="G45" s="62" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" s="49">
+      <c r="B46" s="22" t="n">
+        <v>1213402649</v>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D46" s="53" t="n">
+        <v>46120.40263738426</v>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.1008/2.1008 @ 476.00</t>
+        </is>
+      </c>
+      <c r="F46" s="46" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G46" s="63" t="n">
+        <v>-47.98</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="49">
+      <c r="B47" s="31" t="n">
+        <v>1213402650</v>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D47" s="59" t="n">
+        <v>46120.40263766204</v>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 2/2.1008 @ 476.00</t>
+        </is>
+      </c>
+      <c r="F47" s="47" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G47" s="64" t="n">
+        <v>-952</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48" ht="17" customHeight="1" s="49">
+      <c r="B48" s="39" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C48" s="39" t="inlineStr"/>
+      <c r="D48" s="39" t="inlineStr"/>
+      <c r="E48" s="39" t="inlineStr"/>
+      <c r="F48" s="45" t="inlineStr"/>
+      <c r="G48" s="45" t="n">
+        <v>4179.88</v>
+      </c>
+      <c r="H48" s="48" t="n"/>
+    </row>
+    <row r="49" ht="36.7" customHeight="1" s="49"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:D8"/>
+  </mergeCells>
+  <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="1.36888188976378" header="0.393700787401575" footer="0.393700787401575"/>
+  <pageSetup orientation="landscape" paperSize="0" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0">
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Segoe UI,Regular"&amp;10 &amp;P </oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tests/fixtures/account_ikze_99999999_pl_xlsx_2024-12-31_2026-05-02.xlsx
+++ b/tests/fixtures/account_ikze_99999999_pl_xlsx_2024-12-31_2026-05-02.xlsx
@@ -1062,7 +1062,7 @@
     <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="B4:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
@@ -1131,12 +1131,12 @@
       <c r="D5" s="1" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="n"/>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>99999999</t>
         </is>
       </c>
-      <c r="L5" s="6" t="n"/>
+      <c r="L5" s="11" t="n"/>
       <c r="O5" s="4" t="inlineStr"/>
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="inlineStr"/>
@@ -1185,13 +1185,13 @@
       <c r="F7" s="44" t="n">
         <v>4184.78</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="11" t="n">
         <v>16755.21</v>
       </c>
-      <c r="L7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6" t="n">
+      <c r="L7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="11" t="n">
         <v>4184.78</v>
       </c>
       <c r="R7" s="51" t="n">
@@ -1711,7 +1711,7 @@
     <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="B3:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
@@ -1772,12 +1772,12 @@
       <c r="D4" s="13" t="inlineStr"/>
       <c r="E4" s="13" t="inlineStr"/>
       <c r="F4" s="1" t="n"/>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>99999999</t>
         </is>
       </c>
-      <c r="L4" s="6" t="n"/>
+      <c r="L4" s="11" t="n"/>
       <c r="N4" s="15" t="inlineStr"/>
       <c r="O4" s="15" t="inlineStr"/>
       <c r="P4" s="15" t="inlineStr"/>
@@ -1820,16 +1820,16 @@
       <c r="D6" s="13" t="inlineStr"/>
       <c r="E6" s="13" t="inlineStr"/>
       <c r="F6" s="44" t="n">
-        <v>4184.78</v>
-      </c>
-      <c r="I6" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="11" t="n">
         <v>16755.21</v>
       </c>
-      <c r="L6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>4184.78</v>
+      <c r="L6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>1000</v>
       </c>
       <c r="Q6" s="51" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>118.74</v>
       </c>
       <c r="H10" s="52" t="n">
-        <v>133.76</v>
+        <v>140</v>
       </c>
       <c r="I10" s="54" t="n">
         <v>1187.4</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="56" t="n">
-        <v>150.2</v>
+        <v>212.6</v>
       </c>
       <c r="Q10" s="22" t="inlineStr"/>
     </row>
@@ -2452,7 +2452,7 @@
     <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="B3:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
@@ -2503,12 +2503,12 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr"/>
       <c r="D4" s="1" t="n"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>99999999</t>
         </is>
       </c>
-      <c r="J4" s="6" t="n"/>
+      <c r="J4" s="11" t="n"/>
       <c r="L4" s="42" t="inlineStr"/>
       <c r="M4" s="42" t="inlineStr"/>
     </row>
@@ -2547,13 +2547,13 @@
       <c r="D6" s="44" t="n">
         <v>4184.78</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="11" t="n">
         <v>16755.21</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6" t="n">
+      <c r="J6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="11" t="n">
         <v>4184.78</v>
       </c>
       <c r="M6" s="51" t="n">
@@ -2717,7 +2717,7 @@
     <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="B3:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
@@ -2763,14 +2763,14 @@
       <c r="B4" s="13" t="inlineStr"/>
       <c r="C4" s="13" t="inlineStr"/>
       <c r="D4" s="1" t="n"/>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>99999999</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="inlineStr"/>
+      <c r="H4" s="11" t="inlineStr"/>
     </row>
     <row r="5" ht="25.2" customHeight="1" s="49">
       <c r="B5" s="13" t="inlineStr"/>
@@ -2807,13 +2807,13 @@
       <c r="D6" s="44" t="n">
         <v>4184.78</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="11" t="n">
         <v>16755.21</v>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6" t="n">
+      <c r="F6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11" t="n">
         <v>4184.78</v>
       </c>
       <c r="H6" s="51" t="n">
@@ -2871,7 +2871,7 @@
           <t>Amount</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
+      <c r="H9" s="11" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="49">
       <c r="B10" s="22" t="n">
@@ -2894,7 +2894,7 @@
       <c r="G10" s="56" t="n">
         <v>15611.4</v>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
+      <c r="H10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="49">
       <c r="B11" s="31" t="n">
@@ -2921,7 +2921,7 @@
       <c r="G11" s="64" t="n">
         <v>-2268</v>
       </c>
-      <c r="H11" s="6" t="inlineStr"/>
+      <c r="H11" s="11" t="inlineStr"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="49">
       <c r="B12" s="22" t="n">
@@ -2948,7 +2948,7 @@
       <c r="G12" s="63" t="n">
         <v>-2336</v>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="49">
       <c r="B13" s="31" t="n">
@@ -2975,7 +2975,7 @@
       <c r="G13" s="64" t="n">
         <v>-3696.34</v>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
+      <c r="H13" s="11" t="inlineStr"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="49">
       <c r="B14" s="22" t="n">
@@ -3002,7 +3002,7 @@
       <c r="G14" s="63" t="n">
         <v>-3717.31</v>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
+      <c r="H14" s="11" t="inlineStr"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="49">
       <c r="B15" s="31" t="n">
@@ -3025,7 +3025,7 @@
       <c r="G15" s="62" t="n">
         <v>11.01</v>
       </c>
-      <c r="H15" s="6" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="49">
       <c r="B16" s="22" t="n">
@@ -3052,7 +3052,7 @@
       <c r="G16" s="63" t="n">
         <v>-3445.34</v>
       </c>
-      <c r="H16" s="6" t="inlineStr"/>
+      <c r="H16" s="11" t="inlineStr"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="49">
       <c r="B17" s="31" t="n">
@@ -3079,7 +3079,7 @@
       <c r="G17" s="64" t="n">
         <v>-154</v>
       </c>
-      <c r="H17" s="6" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="49">
       <c r="B18" s="22" t="n">
@@ -3102,7 +3102,7 @@
       <c r="G18" s="56" t="n">
         <v>1.39</v>
       </c>
-      <c r="H18" s="6" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="49">
       <c r="B19" s="31" t="n">
@@ -3129,7 +3129,7 @@
       <c r="G19" s="62" t="n">
         <v>200.96</v>
       </c>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="49">
       <c r="B20" s="22" t="n">
@@ -3156,7 +3156,7 @@
       <c r="G20" s="56" t="n">
         <v>12.56</v>
       </c>
-      <c r="H20" s="6" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="49">
       <c r="B21" s="31" t="n">
@@ -3183,7 +3183,7 @@
       <c r="G21" s="62" t="n">
         <v>143.92</v>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="49">
       <c r="B22" s="22" t="n">
@@ -3210,7 +3210,7 @@
       <c r="G22" s="56" t="n">
         <v>3445.34</v>
       </c>
-      <c r="H22" s="6" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="49">
       <c r="B23" s="31" t="n">
@@ -3237,7 +3237,7 @@
       <c r="G23" s="62" t="n">
         <v>156.45</v>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
+      <c r="H23" s="11" t="inlineStr"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="49">
       <c r="B24" s="22" t="n">
@@ -3264,7 +3264,7 @@
       <c r="G24" s="63" t="n">
         <v>-988.29</v>
       </c>
-      <c r="H24" s="6" t="inlineStr"/>
+      <c r="H24" s="11" t="inlineStr"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="49">
       <c r="B25" s="31" t="n">
@@ -3291,7 +3291,7 @@
       <c r="G25" s="64" t="n">
         <v>-11.68</v>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="49">
       <c r="B26" s="22" t="n">
@@ -3318,7 +3318,7 @@
       <c r="G26" s="56" t="n">
         <v>541.25</v>
       </c>
-      <c r="H26" s="6" t="inlineStr"/>
+      <c r="H26" s="11" t="inlineStr"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="49">
       <c r="B27" s="31" t="n">
@@ -3345,7 +3345,7 @@
       <c r="G27" s="62" t="n">
         <v>3717.31</v>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="49">
       <c r="B28" s="22" t="n">
@@ -3368,7 +3368,7 @@
       <c r="G28" s="56" t="n">
         <v>5.3</v>
       </c>
-      <c r="H28" s="6" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="49">
       <c r="B29" s="31" t="n">
@@ -3391,7 +3391,7 @@
       <c r="G29" s="62" t="n">
         <v>9.98</v>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="49">
       <c r="B30" s="22" t="n">
@@ -3418,7 +3418,7 @@
       <c r="G30" s="63" t="n">
         <v>-1996</v>
       </c>
-      <c r="H30" s="6" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="49">
       <c r="B31" s="31" t="n">
@@ -3441,7 +3441,7 @@
       <c r="G31" s="62" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="H31" s="6" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr"/>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="49">
       <c r="B32" s="22" t="n">
@@ -3468,7 +3468,7 @@
       <c r="G32" s="63" t="n">
         <v>-49.56</v>
       </c>
-      <c r="H32" s="6" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr"/>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="49">
       <c r="B33" s="31" t="n">
@@ -3495,7 +3495,7 @@
       <c r="G33" s="64" t="n">
         <v>-950.4</v>
       </c>
-      <c r="H33" s="6" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="49">
       <c r="B34" s="22" t="n">
@@ -3522,7 +3522,7 @@
       <c r="G34" s="63" t="n">
         <v>-154.17</v>
       </c>
-      <c r="H34" s="6" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr"/>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="49">
       <c r="B35" s="31" t="n">
@@ -3549,7 +3549,7 @@
       <c r="G35" s="64" t="n">
         <v>-845.85</v>
       </c>
-      <c r="H35" s="6" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr"/>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="49">
       <c r="B36" s="22" t="n">
@@ -3576,7 +3576,7 @@
       <c r="G36" s="63" t="n">
         <v>-147.42</v>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr"/>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="49">
       <c r="B37" s="31" t="n">
@@ -3603,7 +3603,7 @@
       <c r="G37" s="64" t="n">
         <v>-852.61</v>
       </c>
-      <c r="H37" s="6" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="49">
       <c r="B38" s="22" t="n">
@@ -3626,7 +3626,7 @@
       <c r="G38" s="56" t="n">
         <v>5.83</v>
       </c>
-      <c r="H38" s="6" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr"/>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="49">
       <c r="B39" s="31" t="n">
@@ -3653,7 +3653,7 @@
       <c r="G39" s="64" t="n">
         <v>-163.2</v>
       </c>
-      <c r="H39" s="6" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="49">
       <c r="B40" s="22" t="n">
@@ -3680,7 +3680,7 @@
       <c r="G40" s="56" t="n">
         <v>1996</v>
       </c>
-      <c r="H40" s="6" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="49">
       <c r="B41" s="31" t="n">
@@ -3707,7 +3707,7 @@
       <c r="G41" s="64" t="n">
         <v>-2.1</v>
       </c>
-      <c r="H41" s="6" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="49">
       <c r="B42" s="22" t="n">
@@ -3734,7 +3734,7 @@
       <c r="G42" s="56" t="n">
         <v>2268</v>
       </c>
-      <c r="H42" s="6" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="49">
       <c r="B43" s="31" t="n">
@@ -3757,7 +3757,7 @@
       <c r="G43" s="62" t="n">
         <v>3.36</v>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="49">
       <c r="B44" s="22" t="n">
@@ -3784,7 +3784,7 @@
       <c r="G44" s="63" t="n">
         <v>-1187.4</v>
       </c>
-      <c r="H44" s="6" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr"/>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="49">
       <c r="B45" s="31" t="n">
@@ -3807,7 +3807,7 @@
       <c r="G45" s="62" t="n">
         <v>6.11</v>
       </c>
-      <c r="H45" s="6" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr"/>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="49">
       <c r="B46" s="22" t="n">
@@ -3834,7 +3834,7 @@
       <c r="G46" s="63" t="n">
         <v>-47.98</v>
       </c>
-      <c r="H46" s="6" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr"/>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="49">
       <c r="B47" s="31" t="n">
@@ -3861,7 +3861,7 @@
       <c r="G47" s="64" t="n">
         <v>-952</v>
       </c>
-      <c r="H47" s="6" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr"/>
     </row>
     <row r="48" ht="17" customHeight="1" s="49">
       <c r="B48" s="39" t="inlineStr">

--- a/tests/fixtures/account_ikze_99999999_pl_xlsx_2024-12-31_2026-05-02.xlsx
+++ b/tests/fixtures/account_ikze_99999999_pl_xlsx_2024-12-31_2026-05-02.xlsx
@@ -2,44 +2,174 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="120" windowWidth="18060" windowHeight="7050" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CLOSED POSITION HISTORY" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="OPEN POSITION 02052026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PENDING ORDERS HISTORY" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PENDING ORDERS HISTORY " sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="CASH OPERATION HISTORY" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'CLOSED POSITION HISTORY'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'OPEN POSITION 02052026'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'PENDING ORDERS HISTORY '!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'CASH OPERATION HISTORY'!$1:$2</definedName>
+  </definedNames>
+  <calcPr calcId="125725" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="[$-010809]dd/mm/yyyy hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="[$-010809]0.00;(0.00)"/>
+    <numFmt numFmtId="166" formatCode="[$-010809]0.0000;(0.0000)"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font/>
+    <font>
+      <name val="Segoe UI"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <strike val="0"/>
+      <color rgb="FFD3D3D3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FFD3D3D3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <strike val="0"/>
+      <color rgb="FFD3D3D3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FFD3D3D3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FFD3D3D3"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF5CCC81"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FFFF3B2E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <strike val="0"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F4F4"/>
+        <bgColor rgb="FFF3F4F4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -47,16 +177,229 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="67">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -70,11 +413,11 @@
       <rgbColor rgb="00FF00FF"/>
       <rgbColor rgb="0000FFFF"/>
       <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00D3D3D3"/>
       <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00F3F4F4"/>
+      <rgbColor rgb="005CCC81"/>
+      <rgbColor rgb="00FF3B2E"/>
       <rgbColor rgb="00FF00FF"/>
       <rgbColor rgb="0000FFFF"/>
       <rgbColor rgb="00800000"/>
@@ -128,6 +471,306 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>424589</colOff>
+      <row>0</row>
+      <rowOff>393080</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Picture 1"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>20</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>21</col>
+      <colOff>607809</colOff>
+      <row>7</row>
+      <rowOff>546100</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>19</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>19</col>
+      <colOff>424589</colOff>
+      <row>0</row>
+      <rowOff>393080</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Picture 1"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>16</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>16</col>
+      <colOff>1558400</colOff>
+      <row>6</row>
+      <rowOff>546100</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>15</col>
+      <colOff>424589</colOff>
+      <row>0</row>
+      <rowOff>393080</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Picture 1"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>12</col>
+      <colOff>1556688</colOff>
+      <row>6</row>
+      <rowOff>546100</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>10</col>
+      <colOff>424589</colOff>
+      <row>0</row>
+      <rowOff>393080</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Picture 1"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>7</col>
+      <colOff>1473200</colOff>
+      <row>6</row>
+      <rowOff>515761</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,270 +1059,2842 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="B4:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <cols>
+    <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
+    <col width="13.86328125" customWidth="1" style="49" min="2" max="2"/>
+    <col width="10.953125" customWidth="1" style="49" min="3" max="3"/>
+    <col width="7.93359375" customWidth="1" style="49" min="4" max="4"/>
+    <col width="10.78125" customWidth="1" style="49" min="5" max="5"/>
+    <col width="17.18359375" customWidth="1" style="49" min="6" max="6"/>
+    <col width="11.93359375" customWidth="1" style="49" min="7" max="7"/>
+    <col width="17.59375" customWidth="1" style="49" min="8" max="8"/>
+    <col width="13.50390625" customWidth="1" style="49" min="9" max="9"/>
+    <col width="13.4921875" customWidth="1" style="49" min="10" max="10"/>
+    <col width="13.4921875" customWidth="1" style="49" min="11" max="11"/>
+    <col width="10.921875" customWidth="1" style="49" min="12" max="12"/>
+    <col width="11.703125" customWidth="1" style="49" min="13" max="13"/>
+    <col width="11.00390625" customWidth="1" style="49" min="14" max="14"/>
+    <col width="10.80078125" customWidth="1" style="49" min="15" max="15"/>
+    <col width="11.33203125" customWidth="1" style="49" min="16" max="16"/>
+    <col width="18.953125" customWidth="1" style="49" min="17" max="17"/>
+    <col width="16.9921875" customWidth="1" style="49" min="18" max="18"/>
+    <col width="13.4921875" customWidth="1" style="49" min="19" max="19"/>
+    <col width="16.9921875" customWidth="1" style="49" min="20" max="20"/>
+    <col width="14.15234375" customWidth="1" style="49" min="21" max="21"/>
+    <col width="10.26171875" customWidth="1" style="49" min="22" max="22"/>
+    <col width="17.28125" customWidth="1" style="49" min="23" max="23"/>
+    <col width="0.0234375" customWidth="1" style="49" min="24" max="24"/>
+    <col width="2.58203125" customWidth="1" style="49" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.75" customHeight="1" s="49"/>
+    <row r="2" ht="2.25" customHeight="1" s="49"/>
+    <row r="3" ht="2.3" customHeight="1" s="49"/>
+    <row r="4" ht="25.2" customHeight="1" s="49">
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr"/>
+      <c r="D4" s="1" t="inlineStr"/>
+      <c r="E4" s="1" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Name and surname</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="50" t="n">
+        <v>46155.50146462963</v>
+      </c>
+    </row>
+    <row r="5" ht="25.2" customHeight="1" s="49">
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr"/>
+      <c r="D5" s="1" t="inlineStr"/>
+      <c r="E5" s="1" t="inlineStr"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="n"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="25.2" customHeight="1" s="49">
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>Free margin</t>
+        </is>
+      </c>
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>Margin level</t>
+        </is>
+      </c>
+      <c r="U6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="25.2" customHeight="1" s="49">
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="44" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>16755.21</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="11" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="R7" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="43.2" customHeight="1" s="49">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLOSED POSITION HISTORY </t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr"/>
+      <c r="I8" s="15" t="inlineStr"/>
+      <c r="J8" s="15" t="inlineStr"/>
+      <c r="K8" s="15" t="inlineStr"/>
+      <c r="L8" s="15" t="inlineStr"/>
+      <c r="M8" s="15" t="inlineStr"/>
+      <c r="N8" s="15" t="inlineStr"/>
+      <c r="O8" s="15" t="inlineStr"/>
+      <c r="P8" s="15" t="inlineStr"/>
+      <c r="Q8" s="15" t="inlineStr"/>
+      <c r="R8" s="15" t="inlineStr"/>
+      <c r="S8" s="15" t="inlineStr"/>
+      <c r="T8" s="15" t="inlineStr"/>
+    </row>
+    <row r="9" ht="23.75" customHeight="1" s="49">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>31/12/2024 - 02/05/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr"/>
+      <c r="G9" s="15" t="inlineStr"/>
+      <c r="H9" s="15" t="inlineStr"/>
+      <c r="I9" s="15" t="inlineStr"/>
+      <c r="J9" s="15" t="inlineStr"/>
+      <c r="K9" s="15" t="inlineStr"/>
+      <c r="L9" s="15" t="inlineStr"/>
+      <c r="M9" s="15" t="inlineStr"/>
+      <c r="N9" s="15" t="inlineStr"/>
+      <c r="O9" s="15" t="inlineStr"/>
+      <c r="P9" s="15" t="inlineStr"/>
+      <c r="Q9" s="15" t="inlineStr"/>
+      <c r="R9" s="15" t="inlineStr"/>
+      <c r="S9" s="15" t="inlineStr"/>
+      <c r="T9" s="15" t="inlineStr"/>
+      <c r="U9" s="15" t="inlineStr"/>
+    </row>
+    <row r="10" ht="17" customHeight="1" s="49">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Balance :4179.88 - 0.00</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="inlineStr"/>
+      <c r="I10" s="15" t="inlineStr"/>
+      <c r="J10" s="15" t="inlineStr"/>
+      <c r="K10" s="15" t="inlineStr"/>
+      <c r="L10" s="15" t="inlineStr"/>
+      <c r="M10" s="15" t="inlineStr"/>
+      <c r="N10" s="15" t="inlineStr"/>
+      <c r="O10" s="15" t="inlineStr"/>
+      <c r="P10" s="15" t="inlineStr"/>
+      <c r="Q10" s="15" t="inlineStr"/>
+      <c r="R10" s="15" t="inlineStr"/>
+      <c r="S10" s="15" t="inlineStr"/>
+      <c r="T10" s="15" t="inlineStr"/>
+      <c r="U10" s="15" t="inlineStr"/>
+    </row>
+    <row r="11" ht="17" customHeight="1" s="49">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Open price</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>Close time</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Close price</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>Open origin</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>Close origin</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>Purchase value</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>Sale value</t>
+        </is>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="O11" s="18" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="P11" s="18" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="Q11" s="19" t="inlineStr">
+        <is>
+          <t>Commission</t>
+        </is>
+      </c>
+      <c r="R11" s="19" t="inlineStr">
+        <is>
+          <t>Swap</t>
+        </is>
+      </c>
+      <c r="S11" s="19" t="inlineStr">
+        <is>
+          <t>Rollover</t>
+        </is>
+      </c>
+      <c r="T11" s="19" t="inlineStr">
+        <is>
+          <t>Gross P/L</t>
+        </is>
+      </c>
+      <c r="U11" s="18" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="49">
+      <c r="B12" s="22" t="n">
+        <v>900000004</v>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>ASSET07.DE</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="F12" s="53" t="n">
+        <v>45908.37810016204</v>
+      </c>
+      <c r="G12" s="52" t="n">
+        <v>1159.8</v>
+      </c>
+      <c r="H12" s="53" t="n">
+        <v>45943.37802402778</v>
+      </c>
+      <c r="I12" s="52" t="n">
+        <v>1217.2</v>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L12" s="54" t="n">
+        <v>3445.34</v>
+      </c>
+      <c r="M12" s="54" t="n">
+        <v>3589.26</v>
+      </c>
+      <c r="N12" s="22" t="n"/>
+      <c r="O12" s="22" t="n"/>
+      <c r="P12" s="22" t="n"/>
+      <c r="Q12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="56" t="n">
+        <v>143.92</v>
+      </c>
+      <c r="U12" s="22" t="n"/>
+      <c r="V12" s="57" t="n"/>
+      <c r="W12" s="57" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="49">
+      <c r="B13" s="31" t="n">
+        <v>900000005</v>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>ASSET03.UK</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E13" s="58" t="n">
+        <v>14</v>
+      </c>
+      <c r="F13" s="59" t="n">
+        <v>45901.37525900463</v>
+      </c>
+      <c r="G13" s="58" t="n">
+        <v>72.69</v>
+      </c>
+      <c r="H13" s="59" t="n">
+        <v>45951.64296587963</v>
+      </c>
+      <c r="I13" s="58" t="n">
+        <v>83.76000000000001</v>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L13" s="60" t="n">
+        <v>3717.31</v>
+      </c>
+      <c r="M13" s="60" t="n">
+        <v>4258.56</v>
+      </c>
+      <c r="N13" s="31" t="n"/>
+      <c r="O13" s="31" t="n"/>
+      <c r="P13" s="31" t="n"/>
+      <c r="Q13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="62" t="n">
+        <v>541.25</v>
+      </c>
+      <c r="U13" s="31" t="n"/>
+      <c r="V13" s="57" t="n"/>
+      <c r="W13" s="57" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="49">
+      <c r="B14" s="22" t="n">
+        <v>900000006</v>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="53" t="n">
+        <v>46024.4274031713</v>
+      </c>
+      <c r="G14" s="52" t="n">
+        <v>499</v>
+      </c>
+      <c r="H14" s="53" t="n">
+        <v>46073.64598782407</v>
+      </c>
+      <c r="I14" s="52" t="n">
+        <v>458.2</v>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L14" s="54" t="n">
+        <v>1996</v>
+      </c>
+      <c r="M14" s="54" t="n">
+        <v>1832.8</v>
+      </c>
+      <c r="N14" s="22" t="n"/>
+      <c r="O14" s="22" t="n"/>
+      <c r="P14" s="22" t="n"/>
+      <c r="Q14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="63" t="n">
+        <v>-163.2</v>
+      </c>
+      <c r="U14" s="22" t="n"/>
+      <c r="V14" s="57" t="n"/>
+      <c r="W14" s="57" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="49">
+      <c r="B15" s="31" t="n">
+        <v>900000007</v>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>ASSET06.PL</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E15" s="58" t="n">
+        <v>35</v>
+      </c>
+      <c r="F15" s="59" t="n">
+        <v>45891.3750000463</v>
+      </c>
+      <c r="G15" s="58" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="H15" s="59" t="n">
+        <v>46084.37692043981</v>
+      </c>
+      <c r="I15" s="58" t="n">
+        <v>64.73999999999999</v>
+      </c>
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="K15" s="31" t="inlineStr">
+        <is>
+          <t>xStation Mobile iOS</t>
+        </is>
+      </c>
+      <c r="L15" s="60" t="n">
+        <v>2268</v>
+      </c>
+      <c r="M15" s="60" t="n">
+        <v>2265.9</v>
+      </c>
+      <c r="N15" s="31" t="n"/>
+      <c r="O15" s="31" t="n"/>
+      <c r="P15" s="31" t="n"/>
+      <c r="Q15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="64" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="U15" s="31" t="n"/>
+      <c r="V15" s="57" t="n"/>
+      <c r="W15" s="57" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1" s="49">
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="inlineStr"/>
+      <c r="D16" s="39" t="inlineStr"/>
+      <c r="E16" s="39" t="inlineStr"/>
+      <c r="F16" s="39" t="inlineStr"/>
+      <c r="G16" s="39" t="inlineStr"/>
+      <c r="H16" s="39" t="inlineStr"/>
+      <c r="I16" s="39" t="inlineStr"/>
+      <c r="J16" s="39" t="inlineStr"/>
+      <c r="K16" s="39" t="inlineStr"/>
+      <c r="L16" s="39" t="inlineStr"/>
+      <c r="M16" s="39" t="inlineStr"/>
+      <c r="N16" s="39" t="inlineStr"/>
+      <c r="O16" s="39" t="inlineStr"/>
+      <c r="P16" s="39" t="inlineStr"/>
+      <c r="Q16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="45" t="n">
+        <v>519.87</v>
+      </c>
+      <c r="U16" s="39" t="inlineStr"/>
+    </row>
+    <row r="17" ht="0.05" customHeight="1" s="49"/>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="U8:X8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="U7:W7"/>
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="U5:W5"/>
+    <mergeCell ref="U10:W10"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="U6:W6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="R6:T6"/>
+  </mergeCells>
+  <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="1.36888188976378" header="0.393700787401575" footer="0.393700787401575"/>
+  <pageSetup orientation="landscape" paperSize="0" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0">
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Segoe UI,Regular"&amp;10 &amp;P </oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:P10"/>
+  <dimension ref="B3:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
+    <col width="13.86328125" customWidth="1" style="49" min="2" max="2"/>
+    <col width="10.953125" customWidth="1" style="49" min="3" max="3"/>
+    <col width="7.93359375" customWidth="1" style="49" min="4" max="4"/>
+    <col width="10.78125" customWidth="1" style="49" min="5" max="5"/>
+    <col width="17.32421875" customWidth="1" style="49" min="6" max="6"/>
+    <col width="11.93359375" customWidth="1" style="49" min="7" max="7"/>
+    <col width="17.59375" customWidth="1" style="49" min="8" max="8"/>
+    <col width="13.50390625" customWidth="1" style="49" min="9" max="9"/>
+    <col width="13.4921875" customWidth="1" style="49" min="10" max="10"/>
+    <col width="13.4921875" customWidth="1" style="49" min="11" max="11"/>
+    <col width="10.921875" customWidth="1" style="49" min="12" max="12"/>
+    <col width="22.703125" customWidth="1" style="49" min="13" max="13"/>
+    <col width="22.1328125" customWidth="1" style="49" min="14" max="14"/>
+    <col width="13.4921875" customWidth="1" style="49" min="15" max="15"/>
+    <col width="18.953125" customWidth="1" style="49" min="16" max="16"/>
+    <col width="33.97265625" customWidth="1" style="49" min="17" max="17"/>
+    <col width="0.0234375" customWidth="1" style="49" min="18" max="18"/>
+    <col width="14.01171875" customWidth="1" style="49" min="19" max="19"/>
+    <col width="10.26171875" customWidth="1" style="49" min="20" max="20"/>
+    <col width="19.87109375" customWidth="1" style="49" min="21" max="21"/>
+  </cols>
   <sheetData>
-    <row r="3">
-      <c r="B3" s="1" t="n">
-        <v>46144.4375</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="D4" t="inlineStr">
+    <row r="1" ht="31.75" customHeight="1" s="49"/>
+    <row r="2" ht="2.25" customHeight="1" s="49"/>
+    <row r="3" ht="25.2" customHeight="1" s="49">
+      <c r="B3" s="13" t="inlineStr"/>
+      <c r="C3" s="13" t="inlineStr"/>
+      <c r="D3" s="13" t="inlineStr"/>
+      <c r="E3" s="13" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Name and surname</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="inlineStr"/>
+      <c r="O3" s="15" t="inlineStr"/>
+      <c r="P3" s="15" t="inlineStr"/>
+      <c r="Q3" s="50" t="n">
+        <v>46155.501465</v>
+      </c>
+    </row>
+    <row r="4" ht="25.2" customHeight="1" s="49">
+      <c r="B4" s="13" t="inlineStr"/>
+      <c r="C4" s="13" t="inlineStr"/>
+      <c r="D4" s="13" t="inlineStr"/>
+      <c r="E4" s="13" t="inlineStr"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="n"/>
+      <c r="N4" s="15" t="inlineStr"/>
+      <c r="O4" s="15" t="inlineStr"/>
+      <c r="P4" s="15" t="inlineStr"/>
+      <c r="Q4" s="15" t="inlineStr"/>
+    </row>
+    <row r="5" ht="25.2" customHeight="1" s="49">
+      <c r="B5" s="13" t="inlineStr"/>
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="13" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="D5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>Free margin</t>
+        </is>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>Margin level</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.2" customHeight="1" s="49">
+      <c r="B6" s="13" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="13" t="inlineStr"/>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>16755.21</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q6" s="51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="43.2" customHeight="1" s="49">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN POSITION HISTORY </t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="15" t="inlineStr"/>
+      <c r="J7" s="15" t="inlineStr"/>
+      <c r="K7" s="15" t="inlineStr"/>
+      <c r="L7" s="15" t="inlineStr"/>
+      <c r="M7" s="15" t="inlineStr"/>
+      <c r="N7" s="15" t="inlineStr"/>
+      <c r="O7" s="15" t="inlineStr"/>
+      <c r="P7" s="15" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.75" customHeight="1" s="49">
+      <c r="B8" s="65" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F8" s="15" t="inlineStr"/>
+      <c r="G8" s="15" t="inlineStr"/>
+      <c r="H8" s="15" t="inlineStr"/>
+      <c r="I8" s="15" t="inlineStr"/>
+      <c r="J8" s="15" t="inlineStr"/>
+      <c r="K8" s="15" t="inlineStr"/>
+      <c r="L8" s="15" t="inlineStr"/>
+      <c r="M8" s="15" t="inlineStr"/>
+      <c r="N8" s="15" t="inlineStr"/>
+      <c r="O8" s="15" t="inlineStr"/>
+      <c r="P8" s="15" t="inlineStr"/>
+      <c r="Q8" s="15" t="inlineStr"/>
+    </row>
+    <row r="9" ht="17" customHeight="1" s="49">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>Open time</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>Open price</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>Market price</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>Purchase value</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L9" s="18" t="inlineStr">
         <is>
           <t>Margin</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M9" s="19" t="inlineStr">
         <is>
           <t>Commission</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N9" s="19" t="inlineStr">
         <is>
           <t>Swap</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>Rollover</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr">
         <is>
           <t>Gross P/L</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q9" s="18" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1000000001</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>VWCE.DE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="49">
+      <c r="B10" s="22" t="n">
+        <v>900000017</v>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>ASSET05.PL</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46132.375</v>
-      </c>
-      <c r="F8" t="n">
-        <v>100</v>
-      </c>
-      <c r="G8" t="n">
-        <v>110</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I8" t="n">
-        <v>90</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>100</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1000000002</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CNDX.UK</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="E10" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="53" t="n">
+        <v>46086.42805099537</v>
+      </c>
+      <c r="G10" s="52" t="n">
+        <v>118.74</v>
+      </c>
+      <c r="H10" s="52" t="n">
+        <v>140</v>
+      </c>
+      <c r="I10" s="54" t="n">
+        <v>1187.4</v>
+      </c>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="56" t="n">
+        <v>212.6</v>
+      </c>
+      <c r="Q10" s="22" t="inlineStr"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="49">
+      <c r="B11" s="31" t="n">
+        <v>900000018</v>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46142.375</v>
-      </c>
-      <c r="F9" t="n">
-        <v>200</v>
-      </c>
-      <c r="G9" t="n">
-        <v>190</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I9" t="n">
-        <v>180</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-100</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="E11" s="58" t="n">
+        <v>5.9113</v>
+      </c>
+      <c r="F11" s="59" t="n">
+        <v>46044.64063415509</v>
+      </c>
+      <c r="G11" s="58" t="n">
+        <v>39.995</v>
+      </c>
+      <c r="H11" s="58" t="n">
+        <v>41.185</v>
+      </c>
+      <c r="I11" s="60" t="n">
+        <v>1000.02</v>
+      </c>
+      <c r="J11" s="31" t="n"/>
+      <c r="K11" s="31" t="n"/>
+      <c r="L11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="62" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="Q11" s="31" t="inlineStr"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="49">
+      <c r="B12" s="22" t="n">
+        <v>900000019</v>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="n">
+        <v>5.8645</v>
+      </c>
+      <c r="F12" s="53" t="n">
+        <v>46056.42355761574</v>
+      </c>
+      <c r="G12" s="52" t="n">
+        <v>40.205</v>
+      </c>
+      <c r="H12" s="52" t="n">
+        <v>41.185</v>
+      </c>
+      <c r="I12" s="54" t="n">
+        <v>1000.02</v>
+      </c>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="22" t="n"/>
+      <c r="L12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="56" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="Q12" s="22" t="inlineStr"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="49">
+      <c r="B13" s="31" t="n">
+        <v>900000020</v>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E13" s="58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="59" t="n">
+        <v>45908.4788880324</v>
+      </c>
+      <c r="G13" s="58" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="H13" s="58" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="I13" s="60" t="n">
+        <v>154</v>
+      </c>
+      <c r="J13" s="31" t="n"/>
+      <c r="K13" s="31" t="n"/>
+      <c r="L13" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="64" t="n">
+        <v>-40.8</v>
+      </c>
+      <c r="Q13" s="31" t="inlineStr"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="49">
+      <c r="B14" s="22" t="n">
+        <v>900000021</v>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="n">
+        <v>6.0709</v>
+      </c>
+      <c r="F14" s="53" t="n">
+        <v>45950.43493203704</v>
+      </c>
+      <c r="G14" s="52" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="H14" s="52" t="n">
+        <v>41.185</v>
+      </c>
+      <c r="I14" s="54" t="n">
+        <v>999.97</v>
+      </c>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="22" t="n"/>
+      <c r="L14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="56" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="Q14" s="22" t="inlineStr"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="49">
+      <c r="B15" s="31" t="n">
+        <v>900000022</v>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>ASSET01.PL</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E15" s="58" t="n">
+        <v>29</v>
+      </c>
+      <c r="F15" s="59" t="n">
+        <v>45896.37847430556</v>
+      </c>
+      <c r="G15" s="58" t="n">
+        <v>127.46</v>
+      </c>
+      <c r="H15" s="58" t="n">
+        <v>143.58</v>
+      </c>
+      <c r="I15" s="60" t="n">
+        <v>3696.34</v>
+      </c>
+      <c r="J15" s="31" t="n"/>
+      <c r="K15" s="31" t="n"/>
+      <c r="L15" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="62" t="n">
+        <v>467.48</v>
+      </c>
+      <c r="Q15" s="31" t="inlineStr"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="49">
+      <c r="B16" s="22" t="n">
+        <v>900000023</v>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E16" s="52" t="n">
+        <v>2.1043</v>
+      </c>
+      <c r="F16" s="53" t="n">
+        <v>46041.4602808912</v>
+      </c>
+      <c r="G16" s="52" t="n">
+        <v>475.2</v>
+      </c>
+      <c r="H16" s="52" t="n">
+        <v>437.1</v>
+      </c>
+      <c r="I16" s="54" t="n">
+        <v>999.96</v>
+      </c>
+      <c r="J16" s="22" t="n"/>
+      <c r="K16" s="22" t="n"/>
+      <c r="L16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="63" t="n">
+        <v>-80.17</v>
+      </c>
+      <c r="Q16" s="22" t="inlineStr"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="49">
+      <c r="B17" s="31" t="n">
+        <v>900000024</v>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E17" s="58" t="n">
+        <v>64</v>
+      </c>
+      <c r="F17" s="59" t="n">
+        <v>45891.37779449074</v>
+      </c>
+      <c r="G17" s="58" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="H17" s="58" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="I17" s="60" t="n">
+        <v>2336</v>
+      </c>
+      <c r="J17" s="31" t="n"/>
+      <c r="K17" s="31" t="n"/>
+      <c r="L17" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="64" t="n">
+        <v>-524.8</v>
+      </c>
+      <c r="Q17" s="31" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="49">
+      <c r="B18" s="22" t="n">
+        <v>900000025</v>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E18" s="52" t="n">
+        <v>2.1008</v>
+      </c>
+      <c r="F18" s="53" t="n">
+        <v>46120.40263733796</v>
+      </c>
+      <c r="G18" s="52" t="n">
+        <v>476</v>
+      </c>
+      <c r="H18" s="52" t="n">
+        <v>437.1</v>
+      </c>
+      <c r="I18" s="54" t="n">
+        <v>999.98</v>
+      </c>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="63" t="n">
+        <v>-81.72</v>
+      </c>
+      <c r="Q18" s="22" t="inlineStr"/>
+    </row>
+    <row r="19" ht="17" customHeight="1" s="49">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
+      <c r="C19" s="39" t="inlineStr"/>
+      <c r="D19" s="39" t="inlineStr"/>
+      <c r="E19" s="39" t="inlineStr"/>
+      <c r="F19" s="39" t="inlineStr"/>
+      <c r="G19" s="39" t="inlineStr"/>
+      <c r="H19" s="39" t="inlineStr"/>
+      <c r="I19" s="39" t="inlineStr"/>
+      <c r="J19" s="39" t="inlineStr"/>
+      <c r="K19" s="39" t="inlineStr"/>
+      <c r="L19" s="39" t="inlineStr"/>
+      <c r="M19" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="45" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="Q19" s="39" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="17">
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="I6:K6"/>
+  </mergeCells>
+  <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="1.36888188976378" header="0.393700787401575" footer="0.393700787401575"/>
+  <pageSetup orientation="landscape" paperSize="0" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0">
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Segoe UI,Regular"&amp;10 &amp;P </oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="B3:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <cols>
+    <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
+    <col width="13.86328125" customWidth="1" style="49" min="2" max="2"/>
+    <col width="30.00390625" customWidth="1" style="49" min="3" max="3"/>
+    <col width="15.32421875" customWidth="1" style="49" min="4" max="4"/>
+    <col width="11.6015625" customWidth="1" style="49" min="5" max="5"/>
+    <col width="17.59375" customWidth="1" style="49" min="6" max="6"/>
+    <col width="13.4921875" customWidth="1" style="49" min="7" max="7"/>
+    <col width="13.50390625" customWidth="1" style="49" min="8" max="8"/>
+    <col width="13.4921875" customWidth="1" style="49" min="9" max="9"/>
+    <col width="10.921875" customWidth="1" style="49" min="10" max="10"/>
+    <col width="22.703125" customWidth="1" style="49" min="11" max="11"/>
+    <col width="22.1328125" customWidth="1" style="49" min="12" max="12"/>
+    <col width="52.921875" customWidth="1" style="49" min="13" max="13"/>
+    <col width="0.0234375" customWidth="1" style="49" min="14" max="14"/>
+    <col width="29.50390625" customWidth="1" style="49" min="15" max="15"/>
+    <col width="10.26171875" customWidth="1" style="49" min="16" max="16"/>
+    <col width="19.87109375" customWidth="1" style="49" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.75" customHeight="1" s="49"/>
+    <row r="2" ht="2.25" customHeight="1" s="49"/>
+    <row r="3" ht="25.2" customHeight="1" s="49">
+      <c r="B3" s="13" t="inlineStr"/>
+      <c r="C3" s="13" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Name and surname</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="L3" s="42" t="inlineStr"/>
+      <c r="M3" s="66" t="n">
+        <v>46155.50146517361</v>
+      </c>
+    </row>
+    <row r="4" ht="25.2" customHeight="1" s="49">
+      <c r="B4" s="13" t="inlineStr"/>
+      <c r="C4" s="13" t="inlineStr"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="n"/>
+      <c r="L4" s="42" t="inlineStr"/>
+      <c r="M4" s="42" t="inlineStr"/>
+    </row>
+    <row r="5" ht="25.2" customHeight="1" s="49">
+      <c r="B5" s="13" t="inlineStr"/>
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Free margin</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>Margin level</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.2" customHeight="1" s="49">
+      <c r="B6" s="13" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="44" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>16755.21</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="M6" s="51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="43.2" customHeight="1" s="49">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDING ORDERS HISTORY </t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="42" t="inlineStr"/>
+      <c r="H7" s="42" t="inlineStr"/>
+      <c r="I7" s="42" t="inlineStr"/>
+      <c r="J7" s="42" t="inlineStr"/>
+      <c r="K7" s="42" t="inlineStr"/>
+      <c r="L7" s="42" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.75" customHeight="1" s="49">
+      <c r="B8" s="65" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D8" s="44" t="inlineStr"/>
+      <c r="E8" s="44" t="inlineStr"/>
+      <c r="F8" s="44" t="inlineStr"/>
+      <c r="G8" s="44" t="inlineStr"/>
+      <c r="H8" s="44" t="inlineStr"/>
+      <c r="I8" s="44" t="inlineStr"/>
+      <c r="J8" s="44" t="inlineStr"/>
+      <c r="K8" s="44" t="inlineStr"/>
+      <c r="L8" s="44" t="inlineStr"/>
+      <c r="M8" s="44" t="inlineStr"/>
+    </row>
+    <row r="9" ht="17" customHeight="1" s="49">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Purchase value</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Nominal Value</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="M9" s="18" t="inlineStr">
+        <is>
+          <t>Open time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="49">
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+    </row>
+    <row r="11" ht="17" customHeight="1" s="49">
+      <c r="B11" s="39" t="inlineStr"/>
+      <c r="C11" s="45" t="inlineStr"/>
+      <c r="D11" s="45" t="inlineStr"/>
+      <c r="E11" s="45" t="inlineStr"/>
+      <c r="F11" s="45" t="inlineStr"/>
+      <c r="G11" s="45" t="inlineStr"/>
+      <c r="H11" s="45" t="inlineStr"/>
+      <c r="I11" s="45" t="inlineStr"/>
+      <c r="J11" s="45" t="inlineStr"/>
+      <c r="K11" s="45" t="inlineStr"/>
+      <c r="L11" s="45" t="inlineStr"/>
+      <c r="M11" s="45" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="B8:C8"/>
+  </mergeCells>
+  <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="1.36888188976378" header="0.393700787401575" footer="0.393700787401575"/>
+  <pageSetup orientation="landscape" paperSize="0" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0">
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Segoe UI,Regular"&amp;10 &amp;P </oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="B3:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <cols>
+    <col width="1.93359375" customWidth="1" style="49" min="1" max="1"/>
+    <col width="13.86328125" customWidth="1" style="49" min="2" max="2"/>
+    <col width="29.6640625" customWidth="1" style="49" min="3" max="3"/>
+    <col width="27.25390625" customWidth="1" style="49" min="4" max="4"/>
+    <col width="31.08203125" customWidth="1" style="49" min="5" max="5"/>
+    <col width="27.00390625" customWidth="1" style="49" min="6" max="6"/>
+    <col width="33.62109375" customWidth="1" style="49" min="7" max="7"/>
+    <col width="22.12109375" customWidth="1" style="49" min="8" max="8"/>
+    <col width="0.0234375" customWidth="1" style="49" min="9" max="9"/>
+    <col width="82.43359375" customWidth="1" style="49" min="10" max="10"/>
+    <col width="10.26171875" customWidth="1" style="49" min="11" max="11"/>
+    <col width="19.87109375" customWidth="1" style="49" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.75" customHeight="1" s="49"/>
+    <row r="2" ht="2.25" customHeight="1" s="49"/>
+    <row r="3" ht="25.2" customHeight="1" s="49">
+      <c r="B3" s="13" t="inlineStr"/>
+      <c r="C3" s="13" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Name and surname</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="50" t="n">
+        <v>46155.50146535879</v>
+      </c>
+    </row>
+    <row r="4" ht="25.2" customHeight="1" s="49">
+      <c r="B4" s="13" t="inlineStr"/>
+      <c r="C4" s="13" t="inlineStr"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="inlineStr"/>
+      <c r="H4" s="11" t="inlineStr"/>
+    </row>
+    <row r="5" ht="25.2" customHeight="1" s="49">
+      <c r="B5" s="13" t="inlineStr"/>
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Balance</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Free margin</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Margin level</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25.2" customHeight="1" s="49">
+      <c r="B6" s="13" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="44" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>16755.21</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>4184.78</v>
+      </c>
+      <c r="H6" s="51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="43.2" customHeight="1" s="49">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASH OPERATION HISTORY </t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="15" t="inlineStr"/>
+    </row>
+    <row r="8" ht="23.75" customHeight="1" s="49">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>31/12/2024 - 02/05/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr"/>
+      <c r="F8" s="15" t="inlineStr"/>
+      <c r="G8" s="15" t="inlineStr"/>
+      <c r="H8" s="15" t="inlineStr"/>
+    </row>
+    <row r="9" ht="17" customHeight="1" s="49">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="49">
+      <c r="B10" s="22" t="n">
+        <v>905356718</v>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>IKZE Deposit</t>
+        </is>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>45884.5093331713</v>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Transfer in operation on account with id 99999999</t>
+        </is>
+      </c>
+      <c r="F10" s="46" t="n"/>
+      <c r="G10" s="56" t="n">
+        <v>15611.4</v>
+      </c>
+      <c r="H10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="49">
+      <c r="B11" s="31" t="n">
+        <v>910920026</v>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D11" s="59" t="n">
+        <v>45891.37500146991</v>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 35 @ 64.80</t>
+        </is>
+      </c>
+      <c r="F11" s="47" t="inlineStr">
+        <is>
+          <t>ASSET06.PL</t>
+        </is>
+      </c>
+      <c r="G11" s="64" t="n">
+        <v>-2268</v>
+      </c>
+      <c r="H11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="49">
+      <c r="B12" s="22" t="n">
+        <v>910937823</v>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D12" s="53" t="n">
+        <v>45891.37779451389</v>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 64 @ 36.50</t>
+        </is>
+      </c>
+      <c r="F12" s="46" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="G12" s="63" t="n">
+        <v>-2336</v>
+      </c>
+      <c r="H12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="49">
+      <c r="B13" s="31" t="n">
+        <v>914908081</v>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D13" s="59" t="n">
+        <v>45896.3784743287</v>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 29 @ 127.46</t>
+        </is>
+      </c>
+      <c r="F13" s="47" t="inlineStr">
+        <is>
+          <t>ASSET01.PL</t>
+        </is>
+      </c>
+      <c r="G13" s="64" t="n">
+        <v>-3696.34</v>
+      </c>
+      <c r="H13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="49">
+      <c r="B14" s="22" t="n">
+        <v>918882470</v>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D14" s="53" t="n">
+        <v>45901.37532741898</v>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 14 @ 72.6900</t>
+        </is>
+      </c>
+      <c r="F14" s="46" t="inlineStr">
+        <is>
+          <t>ASSET03.UK</t>
+        </is>
+      </c>
+      <c r="G14" s="63" t="n">
+        <v>-3717.31</v>
+      </c>
+      <c r="H14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="49">
+      <c r="B15" s="31" t="n">
+        <v>923989037</v>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D15" s="59" t="n">
+        <v>45903.72320255787</v>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2025-08</t>
+        </is>
+      </c>
+      <c r="F15" s="47" t="n"/>
+      <c r="G15" s="62" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="H15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="49">
+      <c r="B16" s="22" t="n">
+        <v>927390456</v>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D16" s="53" t="n">
+        <v>45908.37810153935</v>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.6956 @ 1159.80</t>
+        </is>
+      </c>
+      <c r="F16" s="46" t="inlineStr">
+        <is>
+          <t>ASSET07.DE</t>
+        </is>
+      </c>
+      <c r="G16" s="63" t="n">
+        <v>-3445.34</v>
+      </c>
+      <c r="H16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="49">
+      <c r="B17" s="31" t="n">
+        <v>927604217</v>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D17" s="59" t="n">
+        <v>45908.47888804398</v>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 4 @ 38.50</t>
+        </is>
+      </c>
+      <c r="F17" s="47" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="G17" s="64" t="n">
+        <v>-154</v>
+      </c>
+      <c r="H17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="49">
+      <c r="B18" s="22" t="n">
+        <v>959579808</v>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D18" s="53" t="n">
+        <v>45933.61075918982</v>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2025-09</t>
+        </is>
+      </c>
+      <c r="F18" s="46" t="n"/>
+      <c r="G18" s="56" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="49">
+      <c r="B19" s="31" t="n">
+        <v>968431370</v>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>DIVIDENT</t>
+        </is>
+      </c>
+      <c r="D19" s="59" t="n">
+        <v>45940.49932527778</v>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>ASSET02.PL PLN 3.1400/ SHR</t>
+        </is>
+      </c>
+      <c r="F19" s="47" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="G19" s="62" t="n">
+        <v>200.96</v>
+      </c>
+      <c r="H19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="49">
+      <c r="B20" s="22" t="n">
+        <v>968437404</v>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>DIVIDENT</t>
+        </is>
+      </c>
+      <c r="D20" s="53" t="n">
+        <v>45940.49933228009</v>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>ASSET02.PL PLN 3.1400/ SHR</t>
+        </is>
+      </c>
+      <c r="F20" s="46" t="inlineStr">
+        <is>
+          <t>ASSET02.PL</t>
+        </is>
+      </c>
+      <c r="G20" s="56" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="H20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="49">
+      <c r="B21" s="31" t="n">
+        <v>970656246</v>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>close trade</t>
+        </is>
+      </c>
+      <c r="D21" s="59" t="n">
+        <v>45943.37802598379</v>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>Profit of position #2011826186</t>
+        </is>
+      </c>
+      <c r="F21" s="47" t="inlineStr">
+        <is>
+          <t>ASSET07.DE</t>
+        </is>
+      </c>
+      <c r="G21" s="62" t="n">
+        <v>143.92</v>
+      </c>
+      <c r="H21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="49">
+      <c r="B22" s="22" t="n">
+        <v>970656247</v>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Stock sale</t>
+        </is>
+      </c>
+      <c r="D22" s="53" t="n">
+        <v>45943.37802598379</v>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>CLOSE BUY 0.6956 @ 1217.20</t>
+        </is>
+      </c>
+      <c r="F22" s="46" t="inlineStr">
+        <is>
+          <t>ASSET07.DE</t>
+        </is>
+      </c>
+      <c r="G22" s="56" t="n">
+        <v>3445.34</v>
+      </c>
+      <c r="H22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="49">
+      <c r="B23" s="31" t="n">
+        <v>976545654</v>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>DIVIDENT</t>
+        </is>
+      </c>
+      <c r="D23" s="59" t="n">
+        <v>45946.33076096065</v>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>ASSET06.PL PLN 4.4700/ SHR</t>
+        </is>
+      </c>
+      <c r="F23" s="47" t="inlineStr">
+        <is>
+          <t>ASSET06.PL</t>
+        </is>
+      </c>
+      <c r="G23" s="62" t="n">
+        <v>156.45</v>
+      </c>
+      <c r="H23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="49">
+      <c r="B24" s="22" t="n">
+        <v>981353624</v>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D24" s="53" t="n">
+        <v>45950.43494649306</v>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 6/6.0709 @ 38.640</t>
+        </is>
+      </c>
+      <c r="F24" s="46" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G24" s="63" t="n">
+        <v>-988.29</v>
+      </c>
+      <c r="H24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="49">
+      <c r="B25" s="31" t="n">
+        <v>981353594</v>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D25" s="59" t="n">
+        <v>45950.43493204861</v>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.0709/6.0709 @ 38.640</t>
+        </is>
+      </c>
+      <c r="F25" s="47" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G25" s="64" t="n">
+        <v>-11.68</v>
+      </c>
+      <c r="H25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="49">
+      <c r="B26" s="22" t="n">
+        <v>983646089</v>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>close trade</t>
+        </is>
+      </c>
+      <c r="D26" s="53" t="n">
+        <v>45951.64297008102</v>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Profit of position #1999508307</t>
+        </is>
+      </c>
+      <c r="F26" s="46" t="inlineStr">
+        <is>
+          <t>ASSET03.UK</t>
+        </is>
+      </c>
+      <c r="G26" s="56" t="n">
+        <v>541.25</v>
+      </c>
+      <c r="H26" s="11" t="inlineStr"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="49">
+      <c r="B27" s="31" t="n">
+        <v>983646090</v>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>Stock sale</t>
+        </is>
+      </c>
+      <c r="D27" s="59" t="n">
+        <v>45951.64297008102</v>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>CLOSE BUY 14 @ 83.7600</t>
+        </is>
+      </c>
+      <c r="F27" s="47" t="inlineStr">
+        <is>
+          <t>ASSET03.UK</t>
+        </is>
+      </c>
+      <c r="G27" s="62" t="n">
+        <v>3717.31</v>
+      </c>
+      <c r="H27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="49">
+      <c r="B28" s="22" t="n">
+        <v>1005869298</v>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D28" s="53" t="n">
+        <v>45967.52538728009</v>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2025-10</t>
+        </is>
+      </c>
+      <c r="F28" s="46" t="n"/>
+      <c r="G28" s="56" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="49">
+      <c r="B29" s="31" t="n">
+        <v>1039472399</v>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D29" s="59" t="n">
+        <v>45995.6207953125</v>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2025-11</t>
+        </is>
+      </c>
+      <c r="F29" s="47" t="n"/>
+      <c r="G29" s="62" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="H29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="49">
+      <c r="B30" s="22" t="n">
+        <v>1071382341</v>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D30" s="53" t="n">
+        <v>46024.42740359954</v>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 4 @ 499.00</t>
+        </is>
+      </c>
+      <c r="F30" s="46" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G30" s="63" t="n">
+        <v>-1996</v>
+      </c>
+      <c r="H30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="49">
+      <c r="B31" s="31" t="n">
+        <v>1078775992</v>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D31" s="59" t="n">
+        <v>46029.59267013889</v>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2025-12</t>
+        </is>
+      </c>
+      <c r="F31" s="47" t="n"/>
+      <c r="G31" s="62" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="49">
+      <c r="B32" s="22" t="n">
+        <v>1095495643</v>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D32" s="53" t="n">
+        <v>46041.46028091435</v>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.1043/2.1043 @ 475.20</t>
+        </is>
+      </c>
+      <c r="F32" s="46" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G32" s="63" t="n">
+        <v>-49.56</v>
+      </c>
+      <c r="H32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" s="49">
+      <c r="B33" s="31" t="n">
+        <v>1095495644</v>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D33" s="59" t="n">
+        <v>46041.46028163195</v>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 2/2.1043 @ 475.20</t>
+        </is>
+      </c>
+      <c r="F33" s="47" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G33" s="64" t="n">
+        <v>-950.4</v>
+      </c>
+      <c r="H33" s="11" t="inlineStr"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" s="49">
+      <c r="B34" s="22" t="n">
+        <v>1101693553</v>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D34" s="53" t="n">
+        <v>46044.64063416667</v>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.9113/5.9113 @ 39.995</t>
+        </is>
+      </c>
+      <c r="F34" s="46" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G34" s="63" t="n">
+        <v>-154.17</v>
+      </c>
+      <c r="H34" s="11" t="inlineStr"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="49">
+      <c r="B35" s="31" t="n">
+        <v>1101693625</v>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D35" s="59" t="n">
+        <v>46044.64064701389</v>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 5/5.9113 @ 39.995</t>
+        </is>
+      </c>
+      <c r="F35" s="47" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G35" s="64" t="n">
+        <v>-845.85</v>
+      </c>
+      <c r="H35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1" s="49">
+      <c r="B36" s="22" t="n">
+        <v>1120498401</v>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D36" s="53" t="n">
+        <v>46056.42355762731</v>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.8645/5.8645 @ 40.205</t>
+        </is>
+      </c>
+      <c r="F36" s="46" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G36" s="63" t="n">
+        <v>-147.42</v>
+      </c>
+      <c r="H36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1" s="49">
+      <c r="B37" s="31" t="n">
+        <v>1120498427</v>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D37" s="59" t="n">
+        <v>46056.4235774074</v>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 5/5.8645 @ 40.205</t>
+        </is>
+      </c>
+      <c r="F37" s="47" t="inlineStr">
+        <is>
+          <t>ASSET08.DE</t>
+        </is>
+      </c>
+      <c r="G37" s="64" t="n">
+        <v>-852.61</v>
+      </c>
+      <c r="H37" s="11" t="inlineStr"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1" s="49">
+      <c r="B38" s="22" t="n">
+        <v>1122946080</v>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D38" s="53" t="n">
+        <v>46056.83267230324</v>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2026-01</t>
+        </is>
+      </c>
+      <c r="F38" s="46" t="n"/>
+      <c r="G38" s="56" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="H38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1" s="49">
+      <c r="B39" s="31" t="n">
+        <v>1144927775</v>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>close trade</t>
+        </is>
+      </c>
+      <c r="D39" s="59" t="n">
+        <v>46073.6459884838</v>
+      </c>
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>Profit of position #2263464366</t>
+        </is>
+      </c>
+      <c r="F39" s="47" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G39" s="64" t="n">
+        <v>-163.2</v>
+      </c>
+      <c r="H39" s="11" t="inlineStr"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1" s="49">
+      <c r="B40" s="22" t="n">
+        <v>1144927776</v>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>Stock sale</t>
+        </is>
+      </c>
+      <c r="D40" s="53" t="n">
+        <v>46073.6459884838</v>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>CLOSE BUY 4 @ 458.20</t>
+        </is>
+      </c>
+      <c r="F40" s="46" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G40" s="56" t="n">
+        <v>1996</v>
+      </c>
+      <c r="H40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="49">
+      <c r="B41" s="31" t="n">
+        <v>1157155509</v>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>close trade</t>
+        </is>
+      </c>
+      <c r="D41" s="59" t="n">
+        <v>46084.37692292824</v>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>Profit of position #1985596610</t>
+        </is>
+      </c>
+      <c r="F41" s="47" t="inlineStr">
+        <is>
+          <t>ASSET06.PL</t>
+        </is>
+      </c>
+      <c r="G41" s="64" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="H41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="49">
+      <c r="B42" s="22" t="n">
+        <v>1157155510</v>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>Stock sale</t>
+        </is>
+      </c>
+      <c r="D42" s="53" t="n">
+        <v>46084.37692292824</v>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>CLOSE BUY 35 @ 64.74</t>
+        </is>
+      </c>
+      <c r="F42" s="46" t="inlineStr">
+        <is>
+          <t>ASSET06.PL</t>
+        </is>
+      </c>
+      <c r="G42" s="56" t="n">
+        <v>2268</v>
+      </c>
+      <c r="H42" s="11" t="inlineStr"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="49">
+      <c r="B43" s="31" t="n">
+        <v>1162320718</v>
+      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D43" s="59" t="n">
+        <v>46086.12203777778</v>
+      </c>
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2026-02</t>
+        </is>
+      </c>
+      <c r="F43" s="47" t="n"/>
+      <c r="G43" s="62" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="H43" s="11" t="inlineStr"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="49">
+      <c r="B44" s="22" t="n">
+        <v>1163175003</v>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D44" s="53" t="n">
+        <v>46086.42805105324</v>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 10 @ 118.74</t>
+        </is>
+      </c>
+      <c r="F44" s="46" t="inlineStr">
+        <is>
+          <t>ASSET05.PL</t>
+        </is>
+      </c>
+      <c r="G44" s="63" t="n">
+        <v>-1187.4</v>
+      </c>
+      <c r="H44" s="11" t="inlineStr"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" s="49">
+      <c r="B45" s="31" t="n">
+        <v>1208692466</v>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest</t>
+        </is>
+      </c>
+      <c r="D45" s="59" t="n">
+        <v>46115.74372440972</v>
+      </c>
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>Free-funds Interest 2026-03</t>
+        </is>
+      </c>
+      <c r="F45" s="47" t="n"/>
+      <c r="G45" s="62" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="H45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" s="49">
+      <c r="B46" s="22" t="n">
+        <v>1213402649</v>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D46" s="53" t="n">
+        <v>46120.40263738426</v>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>OPEN BUY 0.1008/2.1008 @ 476.00</t>
+        </is>
+      </c>
+      <c r="F46" s="46" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G46" s="63" t="n">
+        <v>-47.98</v>
+      </c>
+      <c r="H46" s="11" t="inlineStr"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" s="49">
+      <c r="B47" s="31" t="n">
+        <v>1213402650</v>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>Stock purchase</t>
+        </is>
+      </c>
+      <c r="D47" s="59" t="n">
+        <v>46120.40263766204</v>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>OPEN BUY 2/2.1008 @ 476.00</t>
+        </is>
+      </c>
+      <c r="F47" s="47" t="inlineStr">
+        <is>
+          <t>ASSET04.PL</t>
+        </is>
+      </c>
+      <c r="G47" s="64" t="n">
+        <v>-952</v>
+      </c>
+      <c r="H47" s="11" t="inlineStr"/>
+    </row>
+    <row r="48" ht="17" customHeight="1" s="49">
+      <c r="B48" s="39" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C48" s="39" t="inlineStr"/>
+      <c r="D48" s="39" t="inlineStr"/>
+      <c r="E48" s="39" t="inlineStr"/>
+      <c r="F48" s="45" t="inlineStr"/>
+      <c r="G48" s="45" t="n">
+        <v>4179.88</v>
+      </c>
+      <c r="H48" s="48" t="n"/>
+    </row>
+    <row r="49" ht="36.7" customHeight="1" s="49"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B8:D8"/>
+  </mergeCells>
+  <pageMargins left="0.393700787401575" right="0.393700787401575" top="0.393700787401575" bottom="1.36888188976378" header="0.393700787401575" footer="0.393700787401575"/>
+  <pageSetup orientation="landscape" paperSize="0" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0">
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Segoe UI,Regular"&amp;10 &amp;P </oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>